--- a/design/editable/card-editing.xlsx
+++ b/design/editable/card-editing.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>PEAK target: 2.6.b. Source: design/cards.json, mod 0.5.1. All 64 cards are included.</t>
+          <t>PEAK target: 2.6.b. Source: design/cards.json, mod 0.6.0. All 64 cards are included. See card-edit-review.xlsx for your submitted requests and their implementation status.</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Notes flag known limitations. Current code shows the actual modifiers, ability handler and parameters. PackRat is disabled by default.</t>
+          <t>Notes flag known limitations. Current code shows the actual modifiers, ability handler and parameters. Existing Enabled settings are preserved during upgrade.</t>
         </is>
       </c>
     </row>
@@ -689,15 +689,19 @@
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>Piton-Free Fingers</t>
+          <t>Piton Fingers</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>Climbing tires you 12% less.</t>
-        </is>
-      </c>
-      <c r="H2" s="6" t="inlineStr"/>
+          <t>Lose stamina 12% slower when climbing.</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Sprinting stamina drains 12% faster</t>
+        </is>
+      </c>
       <c r="I2" s="6" t="inlineStr"/>
       <c r="J2" s="6" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr"/>
@@ -728,7 +732,7 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Budget Scout Cannon</t>
+          <t>Mini Scout Cannon</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -771,15 +775,19 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Swipity, No Slippity</t>
+          <t>To The Bone</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>You slip and slide 35% less.</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr"/>
+          <t>You take 35% less cold when climbing on blue ice.</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Takes 10% longer to warm back up.</t>
+        </is>
+      </c>
       <c r="I4" s="6" t="inlineStr"/>
       <c r="J4" s="6" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr"/>
@@ -818,7 +826,11 @@
           <t>Hang still on a wall to get 4 stamina back every second.</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Climbing speed is reduced by 30%</t>
+        </is>
+      </c>
       <c r="I5" s="6" t="inlineStr"/>
       <c r="J5" s="6" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr"/>
@@ -854,7 +866,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Double jump: one extra jump in mid-air, every 35 seconds.</t>
+          <t>Double jump: one extra jump in mid-air. (35 second cooldown)</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -943,7 +955,11 @@
           <t>Falls hurt 25% less.</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Dynamite explosions deal 3 times as much Injury.</t>
+        </is>
+      </c>
       <c r="I8" s="6" t="inlineStr"/>
       <c r="J8" s="6" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr"/>
@@ -974,7 +990,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Myres' Long Arm</t>
+          <t>Daddy</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -982,7 +998,11 @@
           <t>Grab walls from 20% farther away.</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Stamina drains 10% faster.</t>
+        </is>
+      </c>
       <c r="I9" s="6" t="inlineStr"/>
       <c r="J9" s="6" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr"/>
@@ -1013,7 +1033,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>Scout Cookie Addiction</t>
+          <t>Cookie Addiction</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1061,13 +1081,17 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Once per biome, when your stamina drops below 20, you get 25 back.</t>
+          <t>Below 20 stamina, press V to restore 25 stamina (5-minute cooldown).</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr"/>
       <c r="I11" s="6" t="inlineStr"/>
       <c r="J11" s="6" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>Manual V; below 20 stamina, restore 25, five-minute cooldown. Key configurable.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="100" customHeight="1">
       <c r="A12" s="4" t="n">
@@ -1103,7 +1127,11 @@
           <t>Sprinting tires you 15% less.</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Climbing uses 15% more stamina.</t>
+        </is>
+      </c>
       <c r="I12" s="6" t="inlineStr"/>
       <c r="J12" s="6" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr"/>
@@ -1134,7 +1162,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Scout's Microbreak</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -1142,7 +1170,11 @@
           <t>Stamina starts coming back 0.3 seconds sooner.</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Stamina bar shrinks 15%</t>
+        </is>
+      </c>
       <c r="I13" s="6" t="inlineStr"/>
       <c r="J13" s="6" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr"/>
@@ -1173,7 +1205,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>Gloom Meditation</t>
+          <t>Meditation</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -1181,7 +1213,11 @@
           <t>Crouch and stay still to get stamina back 35% faster.</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Nothing. You're already crouched down staying still</t>
+        </is>
+      </c>
       <c r="I14" s="6" t="inlineStr"/>
       <c r="J14" s="6" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr"/>
@@ -1212,7 +1248,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Myres Made Me Run</t>
+          <t>I'm getting Scoutmastered</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -1255,7 +1291,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>Endurance Badge Grind</t>
+          <t>Endurance Badge</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -1299,10 +1335,14 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Every time a campfire is lit, get 15 extra (yellow) stamina.</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr"/>
+          <t>Every time a campfire is lit, all your Hunger clears.</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>You can't eat cooked food, even when a teammate feeds you.</t>
+        </is>
+      </c>
       <c r="I17" s="6" t="inlineStr"/>
       <c r="J17" s="6" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr"/>
@@ -1333,17 +1373,17 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>Cool Cucumber Complex</t>
+          <t>Cool, Calm, and Collected.</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>You heat up 50% slower.</t>
+          <t>You burn 50% slower.</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>You get cold 30% faster.</t>
+          <t>You freeze 30% faster.</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr"/>
@@ -1376,17 +1416,17 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Bundled Up Badge</t>
+          <t>Just hot.</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>You get cold 50% slower.</t>
+          <t>You freeze 50% slower.</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>You heat up 30% faster.</t>
+          <t>You burn 30% faster.</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr"/>
@@ -1427,7 +1467,11 @@
           <t>Poison builds up 35% slower.</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>You burn and freeze 25% faster.</t>
+        </is>
+      </c>
       <c r="I20" s="6" t="inlineStr"/>
       <c r="J20" s="6" t="inlineStr"/>
       <c r="K20" s="4" t="inlineStr"/>
@@ -1468,8 +1512,16 @@
       </c>
       <c r="H21" s="6" t="inlineStr"/>
       <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="4" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Pending paired replacement: Mandrakes and Zombies do not affect you; a Zombie spawns somewhere random in the next biome.</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Requested Mandrake/Zombie immunity plus next-biome zombie spawn is pending. The existing spores resistance remains; see docs/card-edit-review.md.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="100" customHeight="1">
       <c r="A22" s="4" t="n">
@@ -1505,7 +1557,11 @@
           <t>New thorns count 40% less.</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Takes twice as long to remove the thorns.</t>
+        </is>
+      </c>
       <c r="I22" s="6" t="inlineStr"/>
       <c r="J22" s="6" t="inlineStr"/>
       <c r="K22" s="4" t="inlineStr">
@@ -1540,7 +1596,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Aloe Aftercare</t>
+          <t>Aloe</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -1548,7 +1604,11 @@
           <t>Once you're out of the heat, it wears off 60% faster.</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>You burn 15% faster.</t>
+        </is>
+      </c>
       <c r="I23" s="6" t="inlineStr"/>
       <c r="J23" s="6" t="inlineStr"/>
       <c r="K23" s="4" t="inlineStr"/>
@@ -1579,7 +1639,7 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Heat Pack Afterglow</t>
+          <t>Heat Pack</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
@@ -1587,7 +1647,11 @@
           <t>Once you're out of the cold, it wears off 60% faster.</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>You freeze 15% faster.</t>
+        </is>
+      </c>
       <c r="I24" s="6" t="inlineStr"/>
       <c r="J24" s="6" t="inlineStr"/>
       <c r="K24" s="4" t="inlineStr"/>
@@ -1623,12 +1687,12 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>While you have 20+ Poison or Spores, climbing tires you 30% less.</t>
+          <t>Above 20 Poison, climbing uses 40% less stamina.</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Poison and Spores wear off 30% slower.</t>
+          <t>Poison wears off 30% slower.</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr"/>
@@ -1661,18 +1725,22 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>BingBong Safety Briefing</t>
+          <t>BingBong</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Hits that aren't falls hurt 20% less.</t>
+          <t>Every 10 minutes while alive, gain Infinite Stamina, Invincibility or Low Gravity for 20 seconds.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr"/>
       <c r="I26" s="6" t="inlineStr"/>
       <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Native timed Infinite Stamina, Invincibility or Low Gravity. Low Gravity is floating, not free flight. Ghost time pauses the ten-minute clock.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="100" customHeight="1">
       <c r="A27" s="4" t="n">
@@ -1700,7 +1768,7 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Medkit Merit Badge</t>
+          <t>Tara</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -1743,17 +1811,17 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>Walk It Off, Scout</t>
+          <t>Walk It Off</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>While you have 20+ Injury, climbing and sprinting tire you 25% less.</t>
+          <t>While you have 20+ Injury, climbing and sprinting use 25% less stamina .</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Every injury hurts 20% more.</t>
+          <t>Every injury hurts 10% more.</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr"/>
@@ -1791,13 +1859,17 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Once per biome, when Poison, Spores or Drowsy reaches 35, 20 of it clears at once.</t>
+          <t>Once per biome, press K when Poison, Spores or Drowsy reaches 35 to clear 20 of the worst one.</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr"/>
       <c r="I29" s="6" t="inlineStr"/>
       <c r="J29" s="6" t="inlineStr"/>
-      <c r="K29" s="4" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Manual K; clear 20 from the worst Poison/Spores/Drowsy status at 35+, once per biome. Key configurable.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="100" customHeight="1">
       <c r="A30" s="4" t="n">
@@ -1825,7 +1897,7 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>BingBong Flight Insurance</t>
+          <t>BingBong Parachute</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -1835,7 +1907,7 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>You come back with 40 Injury and skip your next card pick.</t>
+          <t>If used, prevents the next card pick.</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr"/>
@@ -1912,7 +1984,7 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Curse builds up 70% slower.</t>
+          <t>Reviving does not add Curse.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1950,7 +2022,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Tenacity Tincture</t>
+          <t>Mini  Tenacity</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
@@ -1988,7 +2060,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -1998,19 +2070,19 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>One extra pocket.</t>
+          <t>All carried weight is cut in half, including your backpack and a carried scout.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Everything you carry is 35% heavier.</t>
+          <t>Your third pocket is locked for the rest of the run.</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr"/>
       <c r="J34" s="6" t="inlineStr"/>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>DISABLED: extra pocket is not implemented. If enabled, only the 35% weight penalty works.</t>
+          <t>Now halves total weight and blocks new items in the third pocket; existing items remain retrievable. Enabled by default on a fresh config; previous Enabled=false is preserved.</t>
         </is>
       </c>
     </row>
@@ -2045,10 +2117,14 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Everything you carry is 20% lighter.</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr"/>
+          <t>Items in your hands weigh 25% less.</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Items inside your backpack weigh 10% more.</t>
+        </is>
+      </c>
       <c r="I35" s="6" t="inlineStr"/>
       <c r="J35" s="6" t="inlineStr"/>
       <c r="K35" s="4" t="inlineStr"/>
@@ -2126,7 +2202,11 @@
           <t>Once per biome, the first cooked food you eat isn't used up.</t>
         </is>
       </c>
-      <c r="H37" s="6" t="inlineStr"/>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>Uncooked food cures hunger 50% less.</t>
+        </is>
+      </c>
       <c r="I37" s="6" t="inlineStr"/>
       <c r="J37" s="6" t="inlineStr"/>
       <c r="K37" s="4" t="inlineStr">
@@ -2204,17 +2284,17 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>Lord of the Spools</t>
+          <t>Balright</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>A free rope spool appears for you at each new campfire.</t>
+          <t>A Balloon Bunch appears for you at the next campfire (once per run).</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Climbing tires you 8% more.</t>
+          <t>Every stamina use costs 10% more.</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr"/>
@@ -2296,14 +2376,14 @@
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Your third pocket is locked for the rest of the run.</t>
+          <t>Gain one random, permanent drawback: +15% climbing cost, +15% sprint cost, +20% Injury or +20% Hunger.</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr"/>
       <c r="J41" s="6" t="inlineStr"/>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>Pocket lock keeps items already in the pocket; it blocks new use of that pocket.</t>
+          <t>Two bonus cards and one permanent random penalty. The selected penalty is shown in Current Build and retained in state sync.</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2418,7 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Near a teammate (6 m), climbing tires you both 15% less.</t>
+          <t>Climbing near a teammate uses 15% less stamina for you both.</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
@@ -2376,7 +2456,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Tara's First Aid Badge</t>
+          <t>First Aid Badge</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -2431,7 +2511,11 @@
           <t>Carrying a scout feels 35% lighter.</t>
         </is>
       </c>
-      <c r="H44" s="6" t="inlineStr"/>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>While you carry a passed-out scout, their paused death timer drains at 15% of normal speed (or 15% faster if already draining).</t>
+        </is>
+      </c>
       <c r="I44" s="6" t="inlineStr"/>
       <c r="J44" s="6" t="inlineStr"/>
       <c r="K44" s="4" t="inlineStr"/>
@@ -2470,7 +2554,11 @@
           <t>Huddling warms you 35% more, from 35% farther away.</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr"/>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>With no teammate within 6 m, you get cold 20% faster.</t>
+        </is>
+      </c>
       <c r="I45" s="6" t="inlineStr"/>
       <c r="J45" s="6" t="inlineStr"/>
       <c r="K45" s="4" t="inlineStr"/>
@@ -2506,7 +2594,7 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>The first time you revive a teammate in each biome, you both get 20 extra (yellow) stamina.</t>
+          <t>The first time you revive a teammate in each biome, you both get full extra stamina bar.</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr"/>
@@ -2544,7 +2632,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>Long-Distance Uppies</t>
+          <t>You're alright, you're alright</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -2552,7 +2640,11 @@
           <t>Pull teammates up from 30% farther away.</t>
         </is>
       </c>
-      <c r="H47" s="6" t="inlineStr"/>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>Starting a teammate pull costs you 10 stamina (once per reach).</t>
+        </is>
+      </c>
       <c r="I47" s="6" t="inlineStr"/>
       <c r="J47" s="6" t="inlineStr"/>
       <c r="K47" s="4" t="inlineStr"/>
@@ -2634,7 +2726,11 @@
           <t>Teammates near you (6 m) get stamina back 12% faster.</t>
         </is>
       </c>
-      <c r="H49" s="6" t="inlineStr"/>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>With no teammate within 6 m, every stamina use costs you 10% more.</t>
+        </is>
+      </c>
       <c r="I49" s="6" t="inlineStr"/>
       <c r="J49" s="6" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr"/>
@@ -2675,7 +2771,7 @@
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>Falls hurt 80% more.</t>
+          <t>Falls hurt 40% more.</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr"/>
@@ -2713,12 +2809,12 @@
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>Get 30 extra (yellow) stamina now, and 20 more at every campfire after.</t>
+          <t>Get 30 extra stamina now, and 20 more at every campfire after.</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Get 10 Curse now, and 5 more at every campfire after.</t>
+          <t>Get 10 Curse now, and 2 more at every campfire after.</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr"/>
@@ -2756,7 +2852,7 @@
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>Everything you carry is 10% lighter. In each biome, a 65% chance of 25 extra (yellow) stamina.</t>
+          <t>Everything you carry is 10% lighter. In each biome, a 65% chance of 25 extra stamina.</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
@@ -2799,17 +2895,21 @@
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>Once per biome, press B for 60 extra (yellow) stamina.</t>
+          <t>Once per biome, press B for 60 extra stamina.</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Using it costs you 25 Injury.</t>
+          <t>Using it costs you 15 Injury.</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr"/>
       <c r="J53" s="6" t="inlineStr"/>
-      <c r="K53" s="4" t="inlineStr"/>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>Manual B; spend 15 Injury for 60 bonus stamina, once per biome. Key configurable.</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="100" customHeight="1">
       <c r="A54" s="4" t="n">
@@ -2929,7 +3029,7 @@
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Every injury hurts 75% more.</t>
+          <t>Every injury hurts 50% more.</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr"/>
@@ -3181,7 +3281,11 @@
           <t>You turn to stone 35% slower.</t>
         </is>
       </c>
-      <c r="H62" s="6" t="inlineStr"/>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>Fall damage hurts 15% more</t>
+        </is>
+      </c>
       <c r="I62" s="6" t="inlineStr"/>
       <c r="J62" s="6" t="inlineStr"/>
       <c r="K62" s="4" t="inlineStr"/>
@@ -3212,7 +3316,7 @@
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Myres' Fine Print</t>
+          <t>Fine Print</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
@@ -3255,7 +3359,7 @@
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>Myres' Favorite Scout</t>
+          <t>Scoutmaster</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
@@ -3379,7 +3483,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>[["climbStamina", "mul", 0.88, "always", "self"]]</t>
+          <t>[["climbStamina", "mul", 0.88, "always", "self"], ["sprintStamina", "mul", 1.12, "always", "self"]]</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr"/>
@@ -3421,7 +3525,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>[["slipForce", "mul", 0.65, "always", "self"]]</t>
+          <t>[["coldRate", "mul", 0.65, "climbingColdSurface", "self"], ["coldDecay", "mul", 0.9090909090909091, "always", "self"]]</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr"/>
@@ -3442,7 +3546,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[["climbSpeed", "mul", 0.7, "always", "self"]]</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -3513,7 +3617,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>[["fallInjury", "mul", 0.75, "always", "self"]]</t>
+          <t>[["fallInjury", "mul", 0.75, "always", "self"], ["dynamiteInjury", "mul", 3, "always", "self"]]</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr"/>
@@ -3534,7 +3638,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>[["grabReach", "mul", 1.2, "always", "self"]]</t>
+          <t>[["grabReach", "mul", 1.2, "always", "self"], ["staminaUsage", "mul", 1.1, "always", "self"]]</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr"/>
@@ -3586,7 +3690,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>{"threshold": 0.2, "restore": 0.25}</t>
+          <t>{"threshold": 0.2, "restore": 0.25, "cooldown": 300}</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3705,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>[["sprintStamina", "mul", 0.85, "always", "self"]]</t>
+          <t>[["sprintStamina", "mul", 0.85, "always", "self"], ["climbStamina", "mul", 1.15, "always", "self"]]</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr"/>
@@ -3622,7 +3726,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>[["regenDelay", "add", -0.3, "always", "self"]]</t>
+          <t>[["regenDelay", "add", -0.3, "always", "self"], ["maxStamina", "add", -0.15, "always", "self"]]</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr"/>
@@ -3715,12 +3819,12 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>CampfireBonus</t>
+          <t>CampfireMeal</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>{"bonus": 0.15}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3881,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>[["poisonRate", "mul", 0.65, "always", "self"]]</t>
+          <t>[["poisonRate", "mul", 0.65, "always", "self"], ["heatRate", "mul", 1.25, "always", "self"], ["coldRate", "mul", 1.25, "always", "self"]]</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
@@ -3819,7 +3923,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>[["thornsRate", "mul", 0.6, "always", "self"]]</t>
+          <t>[["thornsRate", "mul", 0.6, "always", "self"], ["thornRemovalTime", "mul", 2, "always", "self"]]</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr"/>
@@ -3840,7 +3944,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>[["heatDecay", "mul", 1.6, "always", "self"]]</t>
+          <t>[["heatDecay", "mul", 1.6, "always", "self"], ["heatRate", "mul", 1.15, "always", "self"]]</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr"/>
@@ -3861,7 +3965,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>[["coldDecay", "mul", 1.6, "always", "self"]]</t>
+          <t>[["coldDecay", "mul", 1.6, "always", "self"], ["coldRate", "mul", 1.15, "always", "self"]]</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr"/>
@@ -3882,7 +3986,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>[["climbStamina", "mul", 0.7, "poisonOrSpores20", "self"], ["poisonDecay", "mul", 0.7, "always", "self"], ["sporesDecay", "mul", 0.7, "always", "self"]]</t>
+          <t>[["climbStamina", "mul", 0.6, "poisonAbove20", "self"], ["poisonDecay", "mul", 0.7, "always", "self"]]</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr"/>
@@ -3903,13 +4007,17 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>[["nonFallInjury", "mul", 0.8, "always", "self"]]</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>MushroomCycle</t>
+        </is>
+      </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"interval": 600, "duration": 20, "lowGravity": 1}</t>
         </is>
       </c>
     </row>
@@ -3945,7 +4053,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>[["climbStamina", "mul", 0.75, "injury20", "self"], ["sprintStamina", "mul", 0.75, "injury20", "self"], ["allInjury", "mul", 1.2, "always", "self"]]</t>
+          <t>[["climbStamina", "mul", 0.75, "injury20", "self"], ["sprintStamina", "mul", 0.75, "injury20", "self"], ["allInjury", "mul", 1.1, "always", "self"]]</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr"/>
@@ -4001,7 +4109,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>{"injury": 0.4}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
@@ -4037,7 +4145,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>[["curseRate", "mul", 0.3, "always", "self"], ["allInjury", "mul", 1.25, "always", "self"]]</t>
+          <t>[["reviveCurse", "mul", 0, "always", "self"], ["allInjury", "mul", 1.25, "always", "self"]]</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr"/>
@@ -4083,12 +4191,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>[["invSlots", "add", 1, "always", "self"], ["itemWeight", "mul", 1.35, "always", "self"]]</t>
+          <t>[["totalWeight", "mul", 0.5, "always", "self"]]</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>PackRat</t>
+          <t>PocketTradeoff</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -4108,7 +4216,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>[["itemWeight", "mul", 0.8, "always", "self"]]</t>
+          <t>[["heldItemWeight", "mul", 0.75, "always", "self"], ["backpackItemWeight", "mul", 1.1, "always", "self"]]</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr"/>
@@ -4150,7 +4258,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[["uncookedFoodHunger", "mul", 0.5, "always", "self"]]</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -4200,17 +4308,17 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>[["climbStamina", "mul", 1.08, "always", "self"]]</t>
+          <t>[["staminaUsage", "mul", 1.1, "always", "self"]]</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>CampfireSpawn</t>
+          <t>NextCampfireSpawn</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>{"item": 0}</t>
+          <t>{"item": 2}</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4368,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>{"bonusCards": 2}</t>
+          <t>{"bonusCards": 2, "climbPenalty": 1.15, "sprintPenalty": 1.15, "injuryPenalty": 1.2, "hungerPenalty": 1.2}</t>
         </is>
       </c>
     </row>
@@ -4317,7 +4425,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>[["carryScoutWeight", "mul", 0.65, "always", "self"]]</t>
+          <t>[["carryScoutWeight", "mul", 0.65, "always", "self"], ["carriedDeathRate", "mul", 1.15, "always", "self"]]</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr"/>
@@ -4338,13 +4446,13 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>[["huddleStrength", "mul", 1.35, "always", "self"]]</t>
+          <t>[["huddleStrength", "mul", 1.35, "always", "self"], ["coldRate", "mul", 1.2, "noTeammateNear", "self"]]</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr"/>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"radius": 6}</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4477,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>{"bonus": 0.2}</t>
+          <t>{"bonus": 1}</t>
         </is>
       </c>
     </row>
@@ -4387,10 +4495,14 @@
           <t>[["helpReach", "mul", 1.3, "always", "self"]]</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr"/>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>HelpCost</t>
+        </is>
+      </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"stamina": 0.1}</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4542,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>[["regenRate", "mul", 1.12, "always", "team"]]</t>
+          <t>[["regenRate", "mul", 1.12, "always", "team"], ["staminaUsage", "mul", 1.1, "noTeammateNear", "self"]]</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr"/>
@@ -4451,7 +4563,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>[["sprintSpeed", "mul", 1.35, "always", "self"], ["jumpHeight", "mul", 1.25, "always", "self"], ["fallInjury", "mul", 1.8, "always", "self"]]</t>
+          <t>[["sprintSpeed", "mul", 1.35, "always", "self"], ["jumpHeight", "mul", 1.25, "always", "self"], ["fallInjury", "mul", 1.4, "always", "self"]]</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr"/>
@@ -4482,7 +4594,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>{"bonusNow": 0.3, "bonusFire": 0.2, "curseNow": 0.1, "curseFire": 0.05}</t>
+          <t>{"bonusNow": 0.3, "bonusFire": 0.2, "curseNow": 0.1, "curseFire": 0.02}</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4644,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>{"bonus": 0.6, "injury": 0.25}</t>
+          <t>{"bonus": 0.6, "injury": 0.15}</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4709,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>[["maxStamina", "add", 0.4, "always", "self"], ["allInjury", "mul", 1.75, "always", "self"]]</t>
+          <t>[["maxStamina", "add", 0.4, "always", "self"], ["allInjury", "mul", 1.5, "always", "self"]]</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr"/>
@@ -4739,7 +4851,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>[["petrifyRate", "mul", 0.65, "always", "self"]]</t>
+          <t>[["petrifyRate", "mul", 0.65, "always", "self"], ["fallInjury", "mul", 1.15, "always", "self"]]</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr"/>

--- a/design/editable/card-editing.xlsx
+++ b/design/editable/card-editing.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>PEAK target: 2.6.b. Source: design/cards.json, mod 0.6.0. All 64 cards are included. See card-edit-review.xlsx for your submitted requests and their implementation status.</t>
+          <t>PEAK target: 2.6.b. Source: design/cards.json, mod 0.6.1. All 64 cards are included. See card-edit-review.xlsx for your submitted requests and their implementation status.</t>
         </is>
       </c>
     </row>
@@ -534,46 +534,70 @@
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Current implementation</t>
+          <t>Ability key placeholder</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Notes flag known limitations. Current code shows the actual modifiers, ability handler and parameters. Existing Enabled settings are preserved during upgrade.</t>
+          <t>Keep {key} in manual card text: the game replaces it with your configured binding. Defaults: Nic of Time V, Discount Cure-All K, Bootleg Scoutmaster Bugle B, Budget Checkpoint Flag N.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Numbers in the code</t>
+          <t>Your own images</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Multiplier 0.8 = 20% less, 1.3 = 30% more. Stamina/status amounts 0.1 = 10 game units; cooldowns/delays are seconds, radii metres, chance 0.65 = 65%.</t>
+          <t>Save &lt;Key&gt;.png in art/cards beside CampfireCards.dll. See card-image-map.csv and docs/card-images.md. Restart PEAK after changing images.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>New ideas</t>
+          <t>Current implementation</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Use New ideas for new card concepts. See docs/effect-feasibility.md for supported effects and what still needs a playtest.</t>
+          <t>Notes flag known limitations. Current code shows the actual modifiers, ability handler and parameters. Existing Enabled settings are preserved during upgrade.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>Numbers in the code</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Multiplier 0.8 = 20% less, 1.3 = 30% more. Stamina/status amounts 0.1 = 10 game units; cooldowns/delays are seconds, radii metres, chance 0.65 = 65%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>New ideas</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Use New ideas for new card concepts. See docs/effect-feasibility.md for supported effects and what still needs a playtest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>Return the file</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Save as .xlsx and send it back. CSV is also provided for Excel, Sheets, LibreOffice or a text editor.</t>
         </is>
@@ -694,12 +718,12 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>Lose stamina 12% slower when climbing.</t>
+          <t>Climbing uses 12% less stamina.</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>Sprinting stamina drains 12% faster</t>
+          <t>Sprinting uses 12% more stamina.</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr"/>
@@ -742,7 +766,7 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>30% more fall damage.</t>
+          <t>Take 30% more fall Injury.</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr"/>
@@ -780,12 +804,12 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>You take 35% less cold when climbing on blue ice.</t>
+          <t>Cold builds 35% slower while climbing blue ice.</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Takes 10% longer to warm back up.</t>
+          <t>Warming up takes 10% longer.</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr"/>
@@ -823,12 +847,12 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Hang still on a wall to get 4 stamina back every second.</t>
+          <t>Hang still on a wall to recover 4 stamina per second.</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Climbing speed is reduced by 30%</t>
+          <t>Climb 30% slower.</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr"/>
@@ -866,12 +890,12 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Double jump: one extra jump in mid-air. (35 second cooldown)</t>
+          <t>Jump again in mid-air for a double jump. Cooldown: 35s.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Each double jump makes you a bit drowsy (+7.5 Drowsy).</t>
+          <t>Each double jump adds 7.5 Drowsy.</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr"/>
@@ -909,12 +933,12 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>You climb 30% faster.</t>
+          <t>Climb 30% faster.</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Climbing tires you 20% more.</t>
+          <t>Climbing uses 20% more stamina.</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr"/>
@@ -952,12 +976,12 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Falls hurt 25% less.</t>
+          <t>Take 25% less fall Injury.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Dynamite explosions deal 3 times as much Injury.</t>
+          <t>Dynamite deals 3 times as much Injury.</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr"/>
@@ -1000,7 +1024,7 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Stamina drains 10% faster.</t>
+          <t>All stamina costs are 10% higher.</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr"/>
@@ -1038,12 +1062,12 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Your stamina bar is 25 longer.</t>
+          <t>Gain 25 maximum stamina.</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>You get hungry 35% faster.</t>
+          <t>Hunger builds 35% faster.</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr"/>
@@ -1081,7 +1105,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Below 20 stamina, press V to restore 25 stamina (5-minute cooldown).</t>
+          <t>Press {key} below 20 stamina to recover 25. Cooldown: 5 min.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr"/>
@@ -1124,7 +1148,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Sprinting tires you 15% less.</t>
+          <t>Sprinting uses 15% less stamina.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -1167,12 +1191,12 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Stamina starts coming back 0.3 seconds sooner.</t>
+          <t>Stamina regeneration starts 0.3s sooner.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Stamina bar shrinks 15%</t>
+          <t>Lose 15 maximum stamina.</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr"/>
@@ -1210,15 +1234,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Crouch and stay still to get stamina back 35% faster.</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Nothing. You're already crouched down staying still</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr"/>
+          <t>Crouch and stay still to recover stamina 35% faster.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>You're already crouched. Take a breather.</t>
+        </is>
+      </c>
       <c r="J14" s="6" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr"/>
     </row>
@@ -1253,12 +1277,12 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>You sprint 25% faster.</t>
+          <t>Sprint 25% faster.</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Your stamina bar is 12.5 shorter.</t>
+          <t>Lose 12.5 maximum stamina.</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr"/>
@@ -1296,7 +1320,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Climb for 3 seconds straight, and the next second of climbing costs 35% less stamina.</t>
+          <t>Climb for 3s straight: climbing uses 35% less stamina for the next 1s.</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr"/>
@@ -1335,12 +1359,12 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Every time a campfire is lit, all your Hunger clears.</t>
+          <t>Each new campfire clears your Hunger.</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>You can't eat cooked food, even when a teammate feeds you.</t>
+          <t>You cannot eat cooked food, including food fed to you.</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr"/>
@@ -1378,12 +1402,12 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>You burn 50% slower.</t>
+          <t>Heat builds 50% slower.</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>You freeze 30% faster.</t>
+          <t>Cold builds 30% faster.</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr"/>
@@ -1421,12 +1445,12 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>You freeze 50% slower.</t>
+          <t>Cold builds 50% slower.</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>You burn 30% faster.</t>
+          <t>Heat builds 30% faster.</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr"/>
@@ -1464,12 +1488,12 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Poison builds up 35% slower.</t>
+          <t>Poison builds 35% slower.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>You burn and freeze 25% faster.</t>
+          <t>Heat and Cold build 25% faster.</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr"/>
@@ -1507,7 +1531,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Spores build up 35% slower.</t>
+          <t>Spores build 35% slower.</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr"/>
@@ -1554,12 +1578,12 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>New thorns count 40% less.</t>
+          <t>New Thorns add 40% less status, rounded up to whole thorns.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>Takes twice as long to remove the thorns.</t>
+          <t>Removing Thorns takes twice as long.</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr"/>
@@ -1601,12 +1625,12 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Once you're out of the heat, it wears off 60% faster.</t>
+          <t>Heat wears off 60% faster.</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>You burn 15% faster.</t>
+          <t>Heat builds 15% faster.</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr"/>
@@ -1644,12 +1668,12 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Once you're out of the cold, it wears off 60% faster.</t>
+          <t>Cold wears off 60% faster.</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>You freeze 15% faster.</t>
+          <t>Cold builds 15% faster.</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr"/>
@@ -1730,7 +1754,7 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Every 10 minutes while alive, gain Infinite Stamina, Invincibility or Low Gravity for 20 seconds.</t>
+          <t>Every 10 min alive: a random 20s burst of Infinite Stamina, Invincibility or Low Gravity.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr"/>
@@ -1773,7 +1797,7 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Bandages and medkits heal you 25% more.</t>
+          <t>Healing items remove 25% more Injury from you.</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr"/>
@@ -1816,12 +1840,12 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>While you have 20+ Injury, climbing and sprinting use 25% less stamina .</t>
+          <t>At 20+ Injury, climbing and sprinting use 25% less stamina.</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Every injury hurts 10% more.</t>
+          <t>Take 10% more Injury.</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr"/>
@@ -1859,7 +1883,7 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Once per biome, press K when Poison, Spores or Drowsy reaches 35 to clear 20 of the worst one.</t>
+          <t>Press {key} at 35+ Poison, Spores or Drowsy to remove 20 from the highest. Once per biome.</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr"/>
@@ -1902,12 +1926,12 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Once per run, a fall that would knock you out puts you back on safe ground instead.</t>
+          <t>Once per run, cancel a fatal fall and return to safe ground.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>If used, prevents the next card pick.</t>
+          <t>Using it skips your next card pick.</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr"/>
@@ -1945,7 +1969,7 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Food fills you up 20% more.</t>
+          <t>Food removes 20% more Hunger.</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr"/>
@@ -1989,7 +2013,7 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Every injury hurts 25% more.</t>
+          <t>Take 25% more Injury.</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr"/>
@@ -2022,12 +2046,12 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Mini  Tenacity</t>
+          <t>Mini Tenacity</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Medical items also clear 7.5 of your worst other status.</t>
+          <t>Medical items also remove 7.5 from your highest other status.</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr"/>
@@ -2070,12 +2094,12 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>All carried weight is cut in half, including your backpack and a carried scout.</t>
+          <t>All carried weight is 50% lighter, including backpacks and scouts.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Your third pocket is locked for the rest of the run.</t>
+          <t>Your third pocket cannot hold new items.</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr"/>
@@ -2117,12 +2141,12 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Items in your hands weigh 25% less.</t>
+          <t>Held items weigh 25% less.</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Items inside your backpack weigh 10% more.</t>
+          <t>Backpack contents weigh 10% more.</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr"/>
@@ -2160,7 +2184,7 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>The item in your hands weighs 35% less.</t>
+          <t>Held items weigh 35% less.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr"/>
@@ -2199,12 +2223,12 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Once per biome, the first cooked food you eat isn't used up.</t>
+          <t>Once per biome, your first cooked meal is not consumed.</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Uncooked food cures hunger 50% less.</t>
+          <t>Uncooked food removes 50% less Hunger.</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr"/>
@@ -2246,12 +2270,12 @@
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>Cooked food fills you up 50% more.</t>
+          <t>Cooked food removes 50% more Hunger.</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Eating uncooked food poisons you a little (+7.5 Poison).</t>
+          <t>Eating cookable food raw adds 7.5 Poison.</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr"/>
@@ -2289,12 +2313,12 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>A Balloon Bunch appears for you at the next campfire (once per run).</t>
+          <t>Get one Balloon Bunch at the next campfire. Once per run.</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Every stamina use costs 10% more.</t>
+          <t>All stamina costs are 10% higher.</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr"/>
@@ -2332,7 +2356,7 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>A free bandage appears for you at each new campfire.</t>
+          <t>Get a Bandage at each new campfire after picking this card.</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr"/>
@@ -2371,12 +2395,12 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Get 2 more random cards right now.</t>
+          <t>Immediately gain 2 random bonus cards.</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Gain one random, permanent drawback: +15% climbing cost, +15% sprint cost, +20% Injury or +20% Hunger.</t>
+          <t>One permanent random penalty: climbing or sprinting cost +15%, Injury +20%, or Hunger buildup +20%.</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr"/>
@@ -2418,12 +2442,12 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Climbing near a teammate uses 15% less stamina for you both.</t>
+          <t>You and teammates within 6 m use 15% less climbing stamina.</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Climbing alone tires you 15% more.</t>
+          <t>With no teammate within 6 m, climbing uses 15% more stamina.</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr"/>
@@ -2461,12 +2485,12 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Healing items you use on teammates heal 60% more.</t>
+          <t>Healing items used on teammates remove 60% more Injury.</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Healing items you use on yourself heal 35% less.</t>
+          <t>Healing items used on yourself remove 35% less Injury.</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr"/>
@@ -2508,12 +2532,12 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Carrying a scout feels 35% lighter.</t>
+          <t>Carried scouts weigh 35% less.</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>While you carry a passed-out scout, their paused death timer drains at 15% of normal speed (or 15% faster if already draining).</t>
+          <t>Their paused death timer drains at 15% of normal speed. Already-active timers drain 15% faster.</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr"/>
@@ -2556,7 +2580,7 @@
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>With no teammate within 6 m, you get cold 20% faster.</t>
+          <t>With no teammate within 6 m, Cold builds 20% faster.</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr"/>
@@ -2594,7 +2618,7 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>The first time you revive a teammate in each biome, you both get full extra stamina bar.</t>
+          <t>First teammate revive by feeding or statue each biome: both gain 100 yellow stamina.</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr"/>
@@ -2642,7 +2666,7 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Starting a teammate pull costs you 10 stamina (once per reach).</t>
+          <t>Starting a pull costs 10 stamina, once per continuous reach.</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr"/>
@@ -2680,12 +2704,12 @@
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>Teammates near you (6 m) take 30% less injury.</t>
+          <t>Teammates within 6 m take 30% less Injury.</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>You take half of what you saved them (at most 10 per hit).</t>
+          <t>You take half the prevented Injury, up to 10 per hit.</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr"/>
@@ -2723,12 +2747,12 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>Teammates near you (6 m) get stamina back 12% faster.</t>
+          <t>Teammates within 6 m recover stamina 12% faster.</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>With no teammate within 6 m, every stamina use costs you 10% more.</t>
+          <t>With no teammate within 6 m, all stamina costs are 10% higher.</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr"/>
@@ -2771,7 +2795,7 @@
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>Falls hurt 40% more.</t>
+          <t>Take 40% more fall Injury.</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr"/>
@@ -2809,12 +2833,12 @@
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>Get 30 extra stamina now, and 20 more at every campfire after.</t>
+          <t>Gain 30 yellow stamina now, then 20 at each later campfire.</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Get 10 Curse now, and 2 more at every campfire after.</t>
+          <t>Gain 10 Curse now, then 2 at each later campfire.</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr"/>
@@ -2852,12 +2876,12 @@
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>Everything you carry is 10% lighter. In each biome, a 65% chance of 25 extra stamina.</t>
+          <t>Inventory items weigh 10% less. Each biome: 65% chance of 25 yellow stamina.</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>Otherwise, you take 20 Injury.</t>
+          <t>A failed roll adds 20 Injury instead.</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr"/>
@@ -2895,12 +2919,12 @@
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>Once per biome, press B for 60 extra stamina.</t>
+          <t>Press {key} to gain 60 yellow stamina. Once per biome.</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Using it costs you 15 Injury.</t>
+          <t>Each use adds 15 Injury.</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr"/>
@@ -2942,12 +2966,12 @@
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>Sprint for 2 seconds and you speed up 30% until you stop.</t>
+          <t>Sprint for 2s to move 30% faster until you stop.</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>Stopping after the speed-up makes you a bit drowsy (+7.5 Drowsy, at most every 30 seconds).</t>
+          <t>Stopping after a boost adds 7.5 Drowsy, at most once every 30s.</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr"/>
@@ -2985,7 +3009,7 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>Falls hurt 15% less, and most of the injury only arrives 20 seconds later.</t>
+          <t>Take 25% of a fall's Injury now and 60% after 20s: 15% less in total.</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr"/>
@@ -3024,12 +3048,12 @@
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>Your stamina bar is 40 longer.</t>
+          <t>Gain 40 maximum stamina.</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Every injury hurts 50% more.</t>
+          <t>Take 50% more Injury.</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr"/>
@@ -3067,12 +3091,12 @@
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>Without a backpack, sprint 30% faster and jump 20% higher.</t>
+          <t>Without a backpack: sprint 30% faster and jump 20% higher.</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>With a backpack, you sprint 15% slower.</t>
+          <t>With a backpack: sprint 15% slower.</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr"/>
@@ -3110,12 +3134,12 @@
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>Get 1 more random card right now (Common to Rare).</t>
+          <t>Immediately gain 1 random bonus card, Common to Rare.</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>Get 10 Curse now, and the next campfire offers you only 1 card.</t>
+          <t>Gain 10 Curse. Your next campfire offers only 1 card.</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr"/>
@@ -3153,7 +3177,7 @@
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>See food, items and luggage within 12 m, even through rock.</t>
+          <t>Mark food, items and luggage within 12 m, even through terrain.</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr"/>
@@ -3196,7 +3220,7 @@
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>Eating while you have 20+ Injury heals 7.5 Injury.</t>
+          <t>At 20+ Injury, eating food removes 7.5 Injury.</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr"/>
@@ -3235,12 +3259,12 @@
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>Once per biome, press N to set an anchor. If you pass out, you wake up there.</t>
+          <t>Press {key} on flat ground: your next pass-out revives you here. Once per biome.</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Your stamina bar is 15 shorter.</t>
+          <t>Lose 15 maximum stamina. The revival leaves 40 Injury.</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr"/>
@@ -3278,12 +3302,12 @@
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>You turn to stone 35% slower.</t>
+          <t>Petrification builds 35% slower.</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>Fall damage hurts 15% more</t>
+          <t>Take 15% more fall Injury.</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr"/>
@@ -3321,12 +3345,12 @@
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>Give up one of your cards: your stamina bar becomes 35 longer.</t>
+          <t>Sacrifice one of your cards to gain 35 maximum stamina.</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Get 5 Curse at every campfire after.</t>
+          <t>Gain 5 Curse at each later campfire.</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr"/>
@@ -3364,7 +3388,7 @@
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>Climbing never tires you, falls never hurt, and you sprint 25% faster.</t>
+          <t>Climbing costs no stamina and falls cause no Injury. Sprint 25% faster.</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr"/>
@@ -3407,7 +3431,7 @@
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>Everyone within 15 m of you (you too) gets a stamina bar 35 longer and takes 60% less injury and statuses. Once per biome, the first scout nearby who passes out is revived.</t>
+          <t>You and scouts within 15 m: maximum stamina +35; Injury and status buildup -60%. Share 1 auto-revive per biome.</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr"/>

--- a/design/editable/card-editing.xlsx
+++ b/design/editable/card-editing.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>PEAK target: 2.6.b. Source: design/cards.json, mod 0.6.5. All 64 cards are included. See card-edit-review.xlsx for your submitted requests and their implementation status.</t>
+          <t>PEAK target: 2.6.b. Source: design/cards.json, mod 0.6.6. All 64 cards are included. See card-edit-review.xlsx for your submitted requests and their implementation status.</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Grab walls from 20% farther away.</t>
+          <t>Grab walls from 40% farther away.</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>[["grabReach", "mul", 1.2, "always", "self"], ["staminaUsage", "mul", 1.1, "always", "self"]]</t>
+          <t>[["grabReach", "mul", 1.4, "always", "self"], ["staminaUsage", "mul", 1.1, "always", "self"]]</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr"/>

--- a/design/editable/card-editing.xlsx
+++ b/design/editable/card-editing.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>PEAK target: 2.6.b. Source: design/cards.json, mod 0.6.6. All 64 cards are included. See card-edit-review.xlsx for your submitted requests and their implementation status.</t>
+          <t>PEAK target: 2.6.b. Source: design/cards.json, mod 0.7.1. All 64 cards are included. See card-edit-review.xlsx for your submitted requests and their implementation status.</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>Sprinting uses 12% more stamina.</t>
+          <t>Sprinting uses 5% more stamina.</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr"/>
@@ -766,7 +766,7 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>Take 30% more fall Injury.</t>
+          <t>Take 15% more fall Injury.</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr"/>
@@ -807,11 +807,7 @@
           <t>Cold builds 35% slower while climbing blue ice.</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Warming up takes 10% longer.</t>
-        </is>
-      </c>
+      <c r="H4" s="6" t="inlineStr"/>
       <c r="I4" s="6" t="inlineStr"/>
       <c r="J4" s="6" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr"/>
@@ -895,7 +891,7 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Each double jump adds 7.5 Drowsy.</t>
+          <t>Each double jump adds 5 Drowsy.</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr"/>
@@ -981,7 +977,7 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Dynamite deals 3 times as much Injury.</t>
+          <t>Dynamite deals 50% more Injury.</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr"/>
@@ -1024,7 +1020,7 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>All stamina costs are 10% higher.</t>
+          <t>All stamina costs are 5% higher.</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr"/>
@@ -1067,7 +1063,7 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Hunger builds 35% faster.</t>
+          <t>Hunger builds 15% faster.</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr"/>
@@ -1105,7 +1101,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Press {key} below 20 stamina to recover 25. Cooldown: 5 min.</t>
+          <t>Press {key} below 20 stamina to recover 30. Cooldown: 3 min.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr"/>
@@ -1153,7 +1149,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Climbing uses 15% more stamina.</t>
+          <t>Climbing uses 5% more stamina.</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr"/>
@@ -1191,12 +1187,12 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Stamina regeneration starts 0.3s sooner.</t>
+          <t>Stamina regeneration starts 0.5s sooner.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Lose 15 maximum stamina.</t>
+          <t>Lose 5 maximum stamina.</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr"/>
@@ -1282,7 +1278,7 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Lose 12.5 maximum stamina.</t>
+          <t>Lose 7.5 maximum stamina.</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr"/>
@@ -1320,7 +1316,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Climb for 3s straight: climbing uses 35% less stamina for the next 1s.</t>
+          <t>Climb for 2s straight: climbing uses 40% less stamina for the next 2s.</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr"/>
@@ -1364,7 +1360,7 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Cooked food removes 25% less Hunger.</t>
+          <t>Cooked food removes 10% less Hunger.</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr"/>
@@ -1411,7 +1407,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Cold builds 30% faster.</t>
+          <t>Cold builds 10% faster.</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr"/>
@@ -1454,7 +1450,7 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Heat builds 30% faster.</t>
+          <t>Heat builds 10% faster.</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr"/>
@@ -1497,7 +1493,7 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Heat and Cold build 25% faster.</t>
+          <t>Heat and Cold build 10% faster.</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr"/>
@@ -1585,11 +1581,7 @@
           <t>New Thorns add 40% less status, rounded to the nearest whole thorn.</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Removing Thorns takes twice as long.</t>
-        </is>
-      </c>
+      <c r="H22" s="6" t="inlineStr"/>
       <c r="I22" s="6" t="inlineStr"/>
       <c r="J22" s="6" t="inlineStr"/>
       <c r="K22" s="4" t="inlineStr">
@@ -1634,7 +1626,7 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Heat builds 15% faster.</t>
+          <t>Heat builds 5% faster.</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr"/>
@@ -1677,7 +1669,7 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Cold builds 15% faster.</t>
+          <t>Cold builds 5% faster.</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr"/>
@@ -1720,7 +1712,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Poison wears off 30% slower.</t>
+          <t>Poison wears off 10% slower.</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr"/>
@@ -1801,7 +1793,7 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Healing items remove 25% more Injury from you.</t>
+          <t>Healing removes 25% more Injury from you.</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr"/>
@@ -1849,7 +1841,7 @@
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Take 10% more Injury.</t>
+          <t>Take 5% more Injury.</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr"/>
@@ -1887,7 +1879,7 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Press {key} at 35+ Poison, Spores or Drowsy to remove 20 from the highest. Once per biome.</t>
+          <t>Press {key} at 25+ Poison, Spores or Drowsy to remove 25 from the highest. Once per biome.</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr"/>
@@ -2019,11 +2011,7 @@
           <t>Reviving does not add Curse.</t>
         </is>
       </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>Take 25% more Injury.</t>
-        </is>
-      </c>
+      <c r="H32" s="6" t="inlineStr"/>
       <c r="I32" s="6" t="inlineStr"/>
       <c r="J32" s="6" t="inlineStr"/>
       <c r="K32" s="4" t="inlineStr"/>
@@ -2149,12 +2137,12 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Held items weigh 25% less.</t>
+          <t>Held items weigh 45% less.</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Backpack contents weigh 10% more.</t>
+          <t>Backpack contents weigh 5% more.</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr"/>
@@ -2236,7 +2224,7 @@
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Uncooked food removes 50% less Hunger.</t>
+          <t>Uncooked food removes 15% less Hunger.</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr"/>
@@ -2283,7 +2271,7 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Eating cookable food raw adds 7.5 Poison.</t>
+          <t>Eating cookable food raw adds 5 Poison.</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr"/>
@@ -2324,11 +2312,7 @@
           <t>Get one Balloon Bunch at the next campfire. Once per run.</t>
         </is>
       </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>All stamina costs are 10% higher.</t>
-        </is>
-      </c>
+      <c r="H39" s="6" t="inlineStr"/>
       <c r="I39" s="6" t="inlineStr"/>
       <c r="J39" s="6" t="inlineStr"/>
       <c r="K39" s="4" t="inlineStr"/>
@@ -2408,7 +2392,7 @@
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>One permanent random penalty: climbing or sprinting cost +15%, Injury +20%, or Hunger buildup +20%.</t>
+          <t>One permanent random penalty: climbing or sprinting cost +10%, Injury +10%, or Hunger buildup +10%. It stays even if you give this card up.</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr"/>
@@ -2450,12 +2434,12 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>You and teammates within 6 m use 15% less climbing stamina.</t>
+          <t>You and teammates within 8 m use 20% less climbing stamina.</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>With no teammate within 6 m, climbing uses 15% more stamina.</t>
+          <t>With no teammate within 8 m, climbing uses 5% more stamina.</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr"/>
@@ -2498,7 +2482,7 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Healing items used on yourself remove 35% less Injury.</t>
+          <t>Healing items used on yourself remove 15% less Injury.</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr"/>
@@ -2543,11 +2527,7 @@
           <t>Carried scouts weigh 35% less.</t>
         </is>
       </c>
-      <c r="H44" s="6" t="inlineStr">
-        <is>
-          <t>Their paused death timer drains at 15% of normal speed. Already-active timers drain 15% faster.</t>
-        </is>
-      </c>
+      <c r="H44" s="6" t="inlineStr"/>
       <c r="I44" s="6" t="inlineStr"/>
       <c r="J44" s="6" t="inlineStr"/>
       <c r="K44" s="4" t="inlineStr">
@@ -2590,11 +2570,7 @@
           <t>Huddling warms you 35% more, from 35% farther away.</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>With no teammate within 6 m, Cold builds 20% faster.</t>
-        </is>
-      </c>
+      <c r="H45" s="6" t="inlineStr"/>
       <c r="I45" s="6" t="inlineStr"/>
       <c r="J45" s="6" t="inlineStr"/>
       <c r="K45" s="4" t="inlineStr"/>
@@ -2678,7 +2654,7 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Starting a pull costs 10 stamina, once per continuous reach.</t>
+          <t>Starting a pull costs a base 5 stamina, once per continuous reach.</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr"/>
@@ -2721,7 +2697,7 @@
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>You take half the prevented Injury, up to 10 per hit.</t>
+          <t>You take a quarter of the prevented Injury, up to 5 per hit.</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr"/>
@@ -2759,14 +2735,10 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>Teammates within 6 m recover stamina 12% faster.</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>With no teammate within 6 m, all stamina costs are 10% higher.</t>
-        </is>
-      </c>
+          <t>You and teammates within 8 m recover stamina 15% faster.</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr"/>
       <c r="I49" s="6" t="inlineStr"/>
       <c r="J49" s="6" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr"/>
@@ -2807,7 +2779,7 @@
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>Take 40% more fall Injury.</t>
+          <t>Take 25% more fall Injury.</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr"/>
@@ -2850,7 +2822,7 @@
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Gain 10 Curse now, then 2 at each later campfire.</t>
+          <t>Gain 5 Curse now, then 1 at each later campfire, up to 10 Curse in total.</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr"/>
@@ -2893,7 +2865,7 @@
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>A failed roll adds 20 Injury instead.</t>
+          <t>A failed roll adds 7.5 Injury instead.</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr"/>
@@ -2983,7 +2955,7 @@
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>Stopping after a boost adds 7.5 Drowsy, at most once every 30s.</t>
+          <t>Stopping after a boost adds 2.5 Drowsy, at most once every 60s.</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr"/>
@@ -3065,7 +3037,7 @@
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Take 50% more Injury.</t>
+          <t>Take 25% more Injury.</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr"/>
@@ -3108,7 +3080,7 @@
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>With a backpack: sprint 15% slower.</t>
+          <t>With a backpack: sprint 5% slower.</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr"/>
@@ -3146,12 +3118,12 @@
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>Immediately gain 1 random bonus card, Common to Rare.</t>
+          <t>Immediately gain 2 random bonus cards, Common to Rare.</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>Gain 10 Curse. Your next campfire offers only 1 card.</t>
+          <t>Gain 5 Curse. Your next campfire offers only 2 cards.</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr"/>
@@ -3276,7 +3248,7 @@
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Lose 15 maximum stamina. The revival leaves 40 Injury.</t>
+          <t>The revival leaves 40 Injury.</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr"/>
@@ -3314,14 +3286,10 @@
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>Petrification builds 35% slower.</t>
-        </is>
-      </c>
-      <c r="H62" s="6" t="inlineStr">
-        <is>
-          <t>Take 15% more fall Injury.</t>
-        </is>
-      </c>
+          <t>Petrification builds 50% slower.</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr"/>
       <c r="I62" s="6" t="inlineStr"/>
       <c r="J62" s="6" t="inlineStr"/>
       <c r="K62" s="4" t="inlineStr"/>
@@ -3362,7 +3330,7 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Gain 5 Curse at each later campfire.</t>
+          <t>Gain 5 Curse when the sacrifice is made.</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr"/>
@@ -3519,7 +3487,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>[["climbStamina", "mul", 0.88, "always", "self"], ["sprintStamina", "mul", 1.12, "always", "self"]]</t>
+          <t>[["climbStamina", "mul", 0.88, "always", "self"], ["sprintStamina", "mul", 1.05, "always", "self"]]</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr"/>
@@ -3540,7 +3508,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>[["jumpHeight", "mul", 1.3, "always", "self"], ["fallInjury", "mul", 1.3, "always", "self"]]</t>
+          <t>[["jumpHeight", "mul", 1.3, "always", "self"], ["fallInjury", "mul", 1.15, "always", "self"]]</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr"/>
@@ -3561,7 +3529,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>[["coldRate", "mul", 0.65, "climbingColdSurface", "self"], ["coldDecay", "mul", 0.9090909090909091, "always", "self"]]</t>
+          <t>[["coldRate", "mul", 0.65, "climbingColdSurface", "self"]]</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr"/>
@@ -3617,7 +3585,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>{"cooldown": 15, "drowsy": 0.075}</t>
+          <t>{"cooldown": 15, "drowsy": 0.05}</t>
         </is>
       </c>
     </row>
@@ -3653,7 +3621,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>[["fallInjury", "mul", 0.75, "always", "self"], ["dynamiteInjury", "mul", 3, "always", "self"]]</t>
+          <t>[["fallInjury", "mul", 0.75, "always", "self"], ["dynamiteInjury", "mul", 1.5, "always", "self"]]</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr"/>
@@ -3674,7 +3642,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>[["grabReach", "mul", 1.4, "always", "self"], ["staminaUsage", "mul", 1.1, "always", "self"]]</t>
+          <t>[["grabReach", "mul", 1.4, "always", "self"], ["staminaUsage", "mul", 1.05, "always", "self"]]</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr"/>
@@ -3695,7 +3663,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>[["maxStamina", "add", 0.25, "always", "self"], ["hungerRate", "mul", 1.35, "always", "self"]]</t>
+          <t>[["maxStamina", "add", 0.25, "always", "self"], ["hungerRate", "mul", 1.15, "always", "self"]]</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr"/>
@@ -3726,7 +3694,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>{"threshold": 0.2, "restore": 0.25, "cooldown": 300}</t>
+          <t>{"threshold": 0.2, "restore": 0.3, "cooldown": 180}</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3709,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>[["sprintStamina", "mul", 0.85, "always", "self"], ["climbStamina", "mul", 1.15, "always", "self"]]</t>
+          <t>[["sprintStamina", "mul", 0.85, "always", "self"], ["climbStamina", "mul", 1.05, "always", "self"]]</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr"/>
@@ -3762,7 +3730,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>[["regenDelay", "add", -0.3, "always", "self"], ["maxStamina", "add", -0.15, "always", "self"]]</t>
+          <t>[["regenDelay", "add", -0.5, "always", "self"], ["maxStamina", "add", -0.05, "always", "self"]]</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr"/>
@@ -3804,7 +3772,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>[["sprintSpeed", "mul", 1.25, "always", "self"], ["maxStamina", "add", -0.125, "always", "self"]]</t>
+          <t>[["sprintSpeed", "mul", 1.25, "always", "self"], ["maxStamina", "add", -0.075, "always", "self"]]</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr"/>
@@ -3825,7 +3793,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>[["climbStamina", "mul", 0.65, "pulseActive", "self"]]</t>
+          <t>[["climbStamina", "mul", 0.6, "pulseActive", "self"]]</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -3835,7 +3803,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>{"buildup": 3, "boost": 1}</t>
+          <t>{"buildup": 2, "boost": 2}</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3818,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>[["cookedFoodHunger", "mul", 0.75, "always", "self"]]</t>
+          <t>[["cookedFoodHunger", "mul", 0.9, "always", "self"]]</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -3875,7 +3843,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>[["heatRate", "mul", 0.5, "always", "self"], ["coldRate", "mul", 1.3, "always", "self"]]</t>
+          <t>[["heatRate", "mul", 0.5, "always", "self"], ["coldRate", "mul", 1.1, "always", "self"]]</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr"/>
@@ -3896,7 +3864,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>[["coldRate", "mul", 0.5, "always", "self"], ["heatRate", "mul", 1.3, "always", "self"]]</t>
+          <t>[["coldRate", "mul", 0.5, "always", "self"], ["heatRate", "mul", 1.1, "always", "self"]]</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr"/>
@@ -3917,7 +3885,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>[["poisonRate", "mul", 0.65, "always", "self"], ["heatRate", "mul", 1.25, "always", "self"], ["coldRate", "mul", 1.25, "always", "self"]]</t>
+          <t>[["poisonRate", "mul", 0.65, "always", "self"], ["heatRate", "mul", 1.1, "always", "self"], ["coldRate", "mul", 1.1, "always", "self"]]</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
@@ -3959,7 +3927,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>[["thornsRate", "mul", 0.6, "always", "self"], ["thornRemovalTime", "mul", 2, "always", "self"]]</t>
+          <t>[["thornsRate", "mul", 0.6, "always", "self"]]</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr"/>
@@ -3980,7 +3948,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>[["heatDecay", "mul", 1.6, "always", "self"], ["heatRate", "mul", 1.15, "always", "self"]]</t>
+          <t>[["heatDecay", "mul", 1.6, "always", "self"], ["heatRate", "mul", 1.05, "always", "self"]]</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr"/>
@@ -4001,7 +3969,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>[["coldDecay", "mul", 1.6, "always", "self"], ["coldRate", "mul", 1.15, "always", "self"]]</t>
+          <t>[["coldDecay", "mul", 1.6, "always", "self"], ["coldRate", "mul", 1.05, "always", "self"]]</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr"/>
@@ -4022,7 +3990,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>[["climbStamina", "mul", 0.6, "poisonAbove20", "self"], ["poisonDecay", "mul", 0.7, "always", "self"]]</t>
+          <t>[["climbStamina", "mul", 0.6, "poisonAbove20", "self"], ["poisonDecay", "mul", 0.9, "always", "self"]]</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr"/>
@@ -4089,7 +4057,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>[["climbStamina", "mul", 0.75, "injury20", "self"], ["sprintStamina", "mul", 0.75, "injury20", "self"], ["allInjury", "mul", 1.1, "always", "self"]]</t>
+          <t>[["climbStamina", "mul", 0.75, "injury20", "self"], ["sprintStamina", "mul", 0.75, "injury20", "self"], ["allInjury", "mul", 1.05, "always", "self"]]</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr"/>
@@ -4120,7 +4088,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>{"threshold": 0.35, "remove": 0.2}</t>
+          <t>{"threshold": 0.25, "remove": 0.25}</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4149,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>[["reviveCurse", "mul", 0, "always", "self"], ["allInjury", "mul", 1.25, "always", "self"]]</t>
+          <t>[["reviveCurse", "mul", 0, "always", "self"]]</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr"/>
@@ -4252,7 +4220,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>[["heldItemWeight", "mul", 0.75, "always", "self"], ["backpackItemWeight", "mul", 1.1, "always", "self"]]</t>
+          <t>[["heldItemWeight", "mul", 0.55, "always", "self"], ["backpackItemWeight", "mul", 1.05, "always", "self"]]</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr"/>
@@ -4294,7 +4262,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>[["uncookedFoodHunger", "mul", 0.5, "always", "self"]]</t>
+          <t>[["uncookedFoodHunger", "mul", 0.85, "always", "self"]]</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -4329,7 +4297,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>{"poison": 0.075}</t>
+          <t>{"poison": 0.05}</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4312,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>[["staminaUsage", "mul", 1.1, "always", "self"]]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -4404,7 +4372,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>{"bonusCards": 2, "climbPenalty": 1.15, "sprintPenalty": 1.15, "injuryPenalty": 1.2, "hungerPenalty": 1.2}</t>
+          <t>{"bonusCards": 2, "climbPenalty": 1.1, "sprintPenalty": 1.1, "injuryPenalty": 1.1, "hungerPenalty": 1.1}</t>
         </is>
       </c>
     </row>
@@ -4419,13 +4387,13 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>[["climbStamina", "mul", 0.85, "always", "team"], ["climbStamina", "mul", 0.85, "teammateNear", "self"], ["climbStamina", "mul", 1.15, "noTeammateNear", "self"]]</t>
+          <t>[["climbStamina", "mul", 0.8, "always", "team"], ["climbStamina", "mul", 0.8, "teammateNear", "self"], ["climbStamina", "mul", 1.05, "noTeammateNear", "self"]]</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>{"radius": 6}</t>
+          <t>{"radius": 8}</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4408,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>[["healGiven", "mul", 1.6, "always", "self"], ["healSelfUse", "mul", 0.65, "always", "self"]]</t>
+          <t>[["healGiven", "mul", 1.6, "always", "self"], ["healSelfUse", "mul", 0.85, "always", "self"]]</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr"/>
@@ -4461,7 +4429,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>[["carryScoutWeight", "mul", 0.65, "always", "self"], ["carriedDeathRate", "mul", 1.15, "always", "self"]]</t>
+          <t>[["carryScoutWeight", "mul", 0.65, "always", "self"]]</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr"/>
@@ -4482,13 +4450,13 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>[["huddleStrength", "mul", 1.35, "always", "self"], ["coldRate", "mul", 1.2, "noTeammateNear", "self"]]</t>
+          <t>[["huddleStrength", "mul", 1.35, "always", "self"]]</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr"/>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>{"radius": 6}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4506,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>{"stamina": 0.1}</t>
+          <t>{"stamina": 0.05}</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4531,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>{"radius": 6, "absorb": 0.5, "cap": 0.1}</t>
+          <t>{"radius": 6, "absorb": 0.25, "cap": 0.05}</t>
         </is>
       </c>
     </row>
@@ -4578,13 +4546,13 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>[["regenRate", "mul", 1.12, "always", "team"], ["staminaUsage", "mul", 1.1, "noTeammateNear", "self"]]</t>
+          <t>[["regenRate", "mul", 1.15, "always", "team"], ["regenRate", "mul", 1.15, "teammateNear", "self"]]</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr"/>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>{"radius": 6}</t>
+          <t>{"radius": 8}</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4567,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>[["sprintSpeed", "mul", 1.35, "always", "self"], ["jumpHeight", "mul", 1.25, "always", "self"], ["fallInjury", "mul", 1.4, "always", "self"]]</t>
+          <t>[["sprintSpeed", "mul", 1.35, "always", "self"], ["jumpHeight", "mul", 1.25, "always", "self"], ["fallInjury", "mul", 1.25, "always", "self"]]</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr"/>
@@ -4630,7 +4598,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>{"bonusNow": 0.3, "bonusFire": 0.2, "curseNow": 0.1, "curseFire": 0.02}</t>
+          <t>{"bonusNow": 0.3, "bonusFire": 0.2, "curseNow": 0.05, "curseFire": 0.01, "curseBudget": 0.1}</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4623,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>{"chance": 0.65, "bonus": 0.25, "injury": 0.2}</t>
+          <t>{"chance": 0.65, "bonus": 0.25, "injury": 0.075}</t>
         </is>
       </c>
     </row>
@@ -4705,7 +4673,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>{"buildup": 2, "drowsy": 0.075, "cooldown": 30}</t>
+          <t>{"buildup": 2, "drowsy": 0.025, "cooldown": 60}</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4713,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>[["maxStamina", "add", 0.4, "always", "self"], ["allInjury", "mul", 1.5, "always", "self"]]</t>
+          <t>[["maxStamina", "add", 0.4, "always", "self"], ["allInjury", "mul", 1.25, "always", "self"]]</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr"/>
@@ -4766,7 +4734,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>[["sprintSpeed", "mul", 1.3, "noBackpack", "self"], ["jumpHeight", "mul", 1.2, "noBackpack", "self"], ["sprintSpeed", "mul", 0.85, "wearingBackpack", "self"]]</t>
+          <t>[["sprintSpeed", "mul", 1.3, "noBackpack", "self"], ["jumpHeight", "mul", 1.2, "noBackpack", "self"], ["sprintSpeed", "mul", 0.95, "wearingBackpack", "self"]]</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr"/>
@@ -4797,7 +4765,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>{"bonusCards": 1, "curse": 0.1}</t>
+          <t>{"bonusCards": 2, "curse": 0.05, "nextOffer": 2}</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4830,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>[["maxStamina", "add", -0.15, "always", "self"]]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -4887,7 +4855,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>[["petrifyRate", "mul", 0.65, "always", "self"], ["fallInjury", "mul", 1.15, "always", "self"]]</t>
+          <t>[["petrifyRate", "mul", 0.5, "always", "self"]]</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr"/>
@@ -4918,7 +4886,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>{"curseFire": 0.05}</t>
+          <t>{"curse": 0.05}</t>
         </is>
       </c>
     </row>

--- a/design/editable/card-editing.xlsx
+++ b/design/editable/card-editing.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>PEAK target: 2.6.b. Source: design/cards.json, mod 0.7.1. All 64 cards are included. See card-edit-review.xlsx for your submitted requests and their implementation status.</t>
+          <t>PEAK target: 2.6.b. Source: design/cards.json, mod 0.7.4. All 64 cards are included. See card-edit-review.xlsx for your submitted requests and their implementation status.</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Stamina regeneration starts 0.5s sooner.</t>
+          <t>Hanging still on a wall drains 75% less stamina.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Crouch and stay still to recover stamina 35% faster.</t>
+          <t>Crouch and stay still for 3s to gain 25 yellow stamina. Once per biome.</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr"/>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>You and teammates within 8 m recover stamina 15% faster.</t>
+          <t>You and teammates within 8 m gain 10 maximum stamina.</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr"/>
@@ -3730,13 +3730,17 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>[["regenDelay", "add", -0.5, "always", "self"], ["maxStamina", "add", -0.05, "always", "self"]]</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
+          <t>[["maxStamina", "add", -0.05, "always", "self"]]</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>HoldRefund</t>
+        </is>
+      </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"refund": 0.75}</t>
         </is>
       </c>
     </row>
@@ -3751,13 +3755,17 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>[["regenRate", "mul", 1.35, "crouchStill", "self"]]</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Meditation</t>
+        </is>
+      </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"hold": 3, "bonus": 0.25}</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4554,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>[["regenRate", "mul", 1.15, "always", "team"], ["regenRate", "mul", 1.15, "teammateNear", "self"]]</t>
+          <t>[["maxStamina", "add", 0.1, "always", "team"], ["maxStamina", "add", 0.1, "teammateNear", "self"]]</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr"/>

--- a/design/editable/card-editing.xlsx
+++ b/design/editable/card-editing.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>PEAK target: 2.6.b. Source: design/cards.json, mod 0.7.4. All 64 cards are included. See card-edit-review.xlsx for your submitted requests and their implementation status.</t>
+          <t>PEAK target: 2.6.b. Source: design/cards.json, mod 0.7.6. All 64 cards are included. See card-edit-review.xlsx for your submitted requests and their implementation status.</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Cold builds 35% slower while climbing blue ice.</t>
+          <t>Cold builds 30% slower, and another 50% slower while climbing blue ice.</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr"/>
@@ -843,12 +843,12 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Hang still on a wall to recover 4 stamina per second.</t>
+          <t>Hang still on a wall to recover 10 stamina per second.</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Climb 30% slower.</t>
+          <t>Climb 10% slower.</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr"/>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Sprinting uses 15% less stamina.</t>
+          <t>Sprinting uses 30% less stamina.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Climbing uses 5% more stamina.</t>
+          <t>You get hungry 10% faster.</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr"/>
@@ -1187,14 +1187,10 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Hanging still on a wall drains 75% less stamina.</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Lose 5 maximum stamina.</t>
-        </is>
-      </c>
+          <t>Hanging still on a wall costs no stamina, and you slip and slide 40% less.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr"/>
       <c r="I13" s="6" t="inlineStr"/>
       <c r="J13" s="6" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr"/>
@@ -1273,12 +1269,12 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Sprint 25% faster.</t>
+          <t>Sprint 35% faster.</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Lose 7.5 maximum stamina.</t>
+          <t>Lose 2.5 maximum stamina.</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr"/>
@@ -1402,7 +1398,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Heat builds 50% slower.</t>
+          <t>Heat builds 70% slower, and you get drowsy 30% slower.</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -1445,7 +1441,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Cold builds 50% slower.</t>
+          <t>Cold builds 70% slower, and huddling warms you 30% more.</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
@@ -1488,7 +1484,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Poison builds 35% slower.</t>
+          <t>Poison builds 70% slower and wears off 50% faster.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1531,7 +1527,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Spores build 35% slower.</t>
+          <t>Spores build 80% slower, and Poison 15% slower.</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr"/>
@@ -1578,7 +1574,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>New Thorns add 40% less status, rounded to the nearest whole thorn.</t>
+          <t>New Thorns add 80% less status, thorns take 50% less time to remove, and hits that are not falls hurt 20% less.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr"/>
@@ -1621,7 +1617,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Heat wears off 60% faster.</t>
+          <t>Heat wears off 150% faster.</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
@@ -1664,7 +1660,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Cold wears off 60% faster.</t>
+          <t>Cold wears off 150% faster.</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1793,7 +1789,7 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Healing removes 25% more Injury from you.</t>
+          <t>Healing removes 60% more Injury from you.</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr"/>
@@ -2180,7 +2176,7 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Held items weigh 35% less.</t>
+          <t>Held items weigh 65% less, and climbing with an item in hand uses 15% less stamina.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr"/>
@@ -2219,7 +2215,7 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Once per biome, your first cooked meal is not consumed.</t>
+          <t>Cooked food fills you up 30% more, and once per biome your first cooked meal is not consumed.</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
@@ -2434,7 +2430,7 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>You and teammates within 8 m use 20% less climbing stamina.</t>
+          <t>You and teammates within 8 m use 10% less climbing stamina.</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
@@ -2477,14 +2473,10 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Healing items used on teammates remove 60% more Injury.</t>
-        </is>
-      </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>Healing items used on yourself remove 15% less Injury.</t>
-        </is>
-      </c>
+          <t>Healing items used on teammates remove 100% more Injury.</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr"/>
       <c r="I43" s="6" t="inlineStr"/>
       <c r="J43" s="6" t="inlineStr"/>
       <c r="K43" s="4" t="inlineStr">
@@ -2524,7 +2516,7 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Carried scouts weigh 35% less.</t>
+          <t>Carried scouts weigh 75% less, and you pull teammates up from 20% farther away.</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr"/>
@@ -2567,7 +2559,7 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Huddling warms you 35% more, from 35% farther away.</t>
+          <t>Huddling warms you 75% more, from farther away, and you get cold 20% slower.</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr"/>
@@ -2817,12 +2809,12 @@
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>Gain 30 yellow stamina now, then 20 at each later campfire.</t>
+          <t>Gain 40 yellow stamina now, then 30 at each later campfire.</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Gain 5 Curse now, then 1 at each later campfire, up to 10 Curse in total.</t>
+          <t>Gain 3 Curse now, then 1 at each later campfire, up to 5 total.</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr"/>
@@ -3529,7 +3521,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>[["coldRate", "mul", 0.65, "climbingColdSurface", "self"]]</t>
+          <t>[["coldRate", "mul", 0.7, "always", "self"], ["coldRate", "mul", 0.5, "climbingColdSurface", "self"]]</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr"/>
@@ -3550,7 +3542,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>[["climbSpeed", "mul", 0.7, "always", "self"]]</t>
+          <t>[["climbSpeed", "mul", 0.9, "always", "self"]]</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -3560,7 +3552,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>{"regenPerSecond": 0.04}</t>
+          <t>{"regenPerSecond": 0.1}</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3701,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>[["sprintStamina", "mul", 0.85, "always", "self"], ["climbStamina", "mul", 1.05, "always", "self"]]</t>
+          <t>[["sprintStamina", "mul", 0.7, "always", "self"], ["hungerRate", "mul", 1.1, "always", "self"]]</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr"/>
@@ -3730,7 +3722,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>[["maxStamina", "add", -0.05, "always", "self"]]</t>
+          <t>[["slipForce", "mul", 0.6, "always", "self"]]</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -3740,7 +3732,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>{"refund": 0.75}</t>
+          <t>{"refund": 1.0}</t>
         </is>
       </c>
     </row>
@@ -3780,7 +3772,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>[["sprintSpeed", "mul", 1.25, "always", "self"], ["maxStamina", "add", -0.075, "always", "self"]]</t>
+          <t>[["sprintSpeed", "mul", 1.35, "always", "self"], ["maxStamina", "add", -0.025, "always", "self"]]</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr"/>
@@ -3851,7 +3843,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>[["heatRate", "mul", 0.5, "always", "self"], ["coldRate", "mul", 1.1, "always", "self"]]</t>
+          <t>[["heatRate", "mul", 0.3, "always", "self"], ["drowsyRate", "mul", 0.7, "always", "self"], ["coldRate", "mul", 1.1, "always", "self"]]</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr"/>
@@ -3872,7 +3864,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>[["coldRate", "mul", 0.5, "always", "self"], ["heatRate", "mul", 1.1, "always", "self"]]</t>
+          <t>[["coldRate", "mul", 0.3, "always", "self"], ["huddleStrength", "mul", 1.3, "always", "self"], ["heatRate", "mul", 1.1, "always", "self"]]</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr"/>
@@ -3893,7 +3885,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>[["poisonRate", "mul", 0.65, "always", "self"], ["heatRate", "mul", 1.1, "always", "self"], ["coldRate", "mul", 1.1, "always", "self"]]</t>
+          <t>[["poisonRate", "mul", 0.3, "always", "self"], ["poisonDecay", "mul", 1.5, "always", "self"], ["heatRate", "mul", 1.1, "always", "self"], ["coldRate", "mul", 1.1, "always", "self"]]</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
@@ -3914,7 +3906,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>[["sporesRate", "mul", 0.65, "always", "self"]]</t>
+          <t>[["sporesRate", "mul", 0.2, "always", "self"], ["poisonRate", "mul", 0.85, "always", "self"]]</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr"/>
@@ -3935,7 +3927,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>[["thornsRate", "mul", 0.6, "always", "self"]]</t>
+          <t>[["thornsRate", "mul", 0.2, "always", "self"], ["thornRemovalTime", "mul", 0.5, "always", "self"], ["nonFallInjury", "mul", 0.8, "always", "self"]]</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr"/>
@@ -3956,7 +3948,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>[["heatDecay", "mul", 1.6, "always", "self"], ["heatRate", "mul", 1.05, "always", "self"]]</t>
+          <t>[["heatDecay", "mul", 2.5, "always", "self"], ["heatRate", "mul", 1.05, "always", "self"]]</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr"/>
@@ -3977,7 +3969,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>[["coldDecay", "mul", 1.6, "always", "self"], ["coldRate", "mul", 1.05, "always", "self"]]</t>
+          <t>[["coldDecay", "mul", 2.5, "always", "self"], ["coldRate", "mul", 1.05, "always", "self"]]</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr"/>
@@ -4044,7 +4036,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>[["healReceived", "mul", 1.25, "always", "self"]]</t>
+          <t>[["healReceived", "mul", 1.6, "always", "self"]]</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr"/>
@@ -4249,7 +4241,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>[["heldItemWeight", "mul", 0.65, "always", "self"]]</t>
+          <t>[["heldItemWeight", "mul", 0.35, "always", "self"], ["climbStamina", "mul", 0.85, "climbingWithItem", "self"]]</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr"/>
@@ -4270,7 +4262,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>[["uncookedFoodHunger", "mul", 0.85, "always", "self"]]</t>
+          <t>[["cookedFoodHunger", "mul", 1.3, "always", "self"], ["uncookedFoodHunger", "mul", 0.85, "always", "self"]]</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -4395,7 +4387,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>[["climbStamina", "mul", 0.8, "always", "team"], ["climbStamina", "mul", 0.8, "teammateNear", "self"], ["climbStamina", "mul", 1.05, "noTeammateNear", "self"]]</t>
+          <t>[["climbStamina", "mul", 0.9, "always", "team"], ["climbStamina", "mul", 0.9, "teammateNear", "self"], ["climbStamina", "mul", 1.05, "noTeammateNear", "self"]]</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr"/>
@@ -4416,7 +4408,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>[["healGiven", "mul", 1.6, "always", "self"], ["healSelfUse", "mul", 0.85, "always", "self"]]</t>
+          <t>[["healGiven", "mul", 2.0, "always", "self"]]</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr"/>
@@ -4437,7 +4429,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>[["carryScoutWeight", "mul", 0.65, "always", "self"]]</t>
+          <t>[["carryScoutWeight", "mul", 0.25, "always", "self"], ["helpReach", "mul", 1.2, "always", "self"]]</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr"/>
@@ -4458,7 +4450,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>[["huddleStrength", "mul", 1.35, "always", "self"]]</t>
+          <t>[["huddleStrength", "mul", 1.75, "always", "self"], ["coldRate", "mul", 0.8, "always", "self"]]</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr"/>
@@ -4606,7 +4598,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>{"bonusNow": 0.3, "bonusFire": 0.2, "curseNow": 0.05, "curseFire": 0.01, "curseBudget": 0.1}</t>
+          <t>{"bonusNow": 0.4, "bonusFire": 0.3, "curseNow": 0.03, "curseFire": 0.01, "curseBudget": 0.05}</t>
         </is>
       </c>
     </row>

--- a/design/editable/card-editing.xlsx
+++ b/design/editable/card-editing.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>PEAK target: 2.6.b. Source: design/cards.json, mod 0.7.6. All 64 cards are included. See card-edit-review.xlsx for your submitted requests and their implementation status.</t>
+          <t>PEAK target: 2.6.b. Source: design/cards.json, mod 0.7.7. All 64 cards are included. See card-edit-review.xlsx for your submitted requests and their implementation status.</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Hanging still on a wall costs no stamina, and you slip and slide 40% less.</t>
+          <t>Hanging still on a wall costs almost no stamina, and you slip and slide 40% less.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>New Thorns add 80% less status, thorns take 50% less time to remove, and hits that are not falls hurt 20% less.</t>
+          <t>New Thorns add 80% less status (at least one thorn always counts), thorns take 50% less time to remove, and hits that are not falls hurt 20% less.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr"/>

--- a/design/editable/card-editing.xlsx
+++ b/design/editable/card-editing.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>PEAK target: 2.6.b. Source: design/cards.json, mod 0.7.7. All 64 cards are included. See card-edit-review.xlsx for your submitted requests and their implementation status.</t>
+          <t>PEAK target: 2.6.b. Source: design/cards.json, mod 0.8.0. All 64 cards are included. See card-edit-review.xlsx for your submitted requests and their implementation status.</t>
         </is>
       </c>
     </row>
@@ -718,12 +718,12 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>Climbing uses 12% less stamina.</t>
+          <t>Climbing uses 18% less stamina.</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>Sprinting uses 5% more stamina.</t>
+          <t>Sprinting uses 10% more stamina.</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr"/>
@@ -766,7 +766,7 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>Take 15% more fall Injury.</t>
+          <t>Take 5% more fall Injury.</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Hang still on a wall to recover 10 stamina per second.</t>
+          <t>Hang still on a wall to recover 5 stamina per second.</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Bing BOING</t>
+          <t>Bing Double Boing</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -889,11 +889,7 @@
           <t>Jump again in mid-air for a double jump. Cooldown: 15s.</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Each double jump adds 5 Drowsy.</t>
-        </is>
-      </c>
+      <c r="H6" s="6" t="inlineStr"/>
       <c r="I6" s="6" t="inlineStr"/>
       <c r="J6" s="6" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr"/>
@@ -934,7 +930,7 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Climbing uses 20% more stamina.</t>
+          <t>Climbing uses 10% more stamina.</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr"/>
@@ -967,7 +963,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>Tenderfoot Insurance</t>
+          <t>Tendiefoot</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -1010,7 +1006,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Daddy</t>
+          <t>Daddy Long Arms</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1058,7 +1054,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Gain 25 maximum stamina.</t>
+          <t>Gain 30 maximum stamina.</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -1101,7 +1097,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Press {key} below 20 stamina to recover 30. Cooldown: 3 min.</t>
+          <t>Press {key} to recover 30 stamina. Cooldown: 5 min.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr"/>
@@ -1139,7 +1135,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>Hasty Badge Training</t>
+          <t>Leg Day Skip</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -1182,7 +1178,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>HOOOOLLLD</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -1226,7 +1222,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Crouch and stay still for 3s to gain 25 yellow stamina. Once per biome.</t>
+          <t>Crouch and stay still for 3s to gain a full bar of yellow stamina. Once per biome.</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr"/>
@@ -1272,11 +1268,7 @@
           <t>Sprint 35% faster.</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>Lose 2.5 maximum stamina.</t>
-        </is>
-      </c>
+      <c r="H15" s="6" t="inlineStr"/>
       <c r="I15" s="6" t="inlineStr"/>
       <c r="J15" s="6" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr"/>
@@ -1312,7 +1304,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Climb for 2s straight: climbing uses 40% less stamina for the next 2s.</t>
+          <t>Climb for 2s straight: climbing uses 40% less stamina for the next 3.5s.</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr"/>
@@ -1346,7 +1338,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Marshmallow Morale</t>
+          <t>Campfire++</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -1354,11 +1346,7 @@
           <t>Each new campfire clears your Hunger.</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Cooked food removes 10% less Hunger.</t>
-        </is>
-      </c>
+      <c r="H17" s="6" t="inlineStr"/>
       <c r="I17" s="6" t="inlineStr"/>
       <c r="J17" s="6" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr">
@@ -1527,7 +1515,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Spores build 80% slower, and Poison 15% slower.</t>
+          <t>Spores build 80% slower, and Poison 45% slower.</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr"/>
@@ -1569,12 +1557,12 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Cactus? What Cactus?</t>
+          <t>Almost Climbable Cactus</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>New Thorns add 80% less status (at least one thorn always counts), thorns take 50% less time to remove, and hits that are not falls hurt 20% less.</t>
+          <t>Thorns hurt 80% less, and can be removed 50% faster.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr"/>
@@ -1703,12 +1691,12 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Above 20 Poison, climbing uses 40% less stamina.</t>
+          <t>Poison that builds up over time (gas, venom, vile food) doesn't affect you.</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Poison wears off 10% slower.</t>
+          <t>Instant poison hits hurt 20% more.</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr"/>
@@ -1726,7 +1714,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1741,7 +1729,7 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>BingBong</t>
+          <t>Bing Boing</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
@@ -1784,12 +1772,12 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Tara</t>
+          <t>TechTara</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Healing removes 60% more Injury from you.</t>
+          <t>Reduces fall damage by 20% and every bandage in your inventory reduces it by 20% more. (Limit 3)</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr"/>
@@ -1832,7 +1820,7 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>At 20+ Injury, climbing and sprinting use 25% less stamina.</t>
+          <t>At 20+ Injury, climbing and sprinting use 35% less stamina.</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
@@ -1921,11 +1909,7 @@
           <t>Once per run, cancel a fatal fall and return to safe ground.</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>Using it skips your next card pick.</t>
-        </is>
-      </c>
+      <c r="H30" s="6" t="inlineStr"/>
       <c r="I30" s="6" t="inlineStr"/>
       <c r="J30" s="6" t="inlineStr"/>
       <c r="K30" s="4" t="inlineStr">
@@ -1960,12 +1944,12 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>Gourmand's Gut</t>
+          <t>Perma-Cooking</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Food removes 20% more Hunger.</t>
+          <t>Food removes 25% more Hunger.</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr"/>
@@ -2004,7 +1988,7 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Reviving does not add Curse.</t>
+          <t>You receive a Book of Bones right now.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr"/>
@@ -2043,7 +2027,7 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Medical items also remove 7.5 from your highest other status.</t>
+          <t>Medical and food items also remove a random amount from your highest other negative status.</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr"/>
@@ -2086,7 +2070,7 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>All carried weight is 50% lighter, including backpacks and scouts.</t>
+          <t>All carried weight is 60% lighter, including backpacks and scouts.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -2171,12 +2155,12 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>Idol Hands</t>
+          <t>Super Idol Hands</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Held items weigh 65% less, and climbing with an item in hand uses 15% less stamina.</t>
+          <t>Held items weigh 75% less.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr"/>
@@ -2215,7 +2199,7 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Cooked food fills you up 30% more, and once per biome your first cooked meal is not consumed.</t>
+          <t>Cooked food fills you up 40% more, and once per biome your first cooked meal is not consumed.</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
@@ -2257,17 +2241,17 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>Cooking Badge Deluxe</t>
+          <t>Cooked</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>Cooked food removes 50% more Hunger.</t>
+          <t>Cooked food removes 60% more Hunger.</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Eating cookable food raw adds 5 Poison.</t>
+          <t>Eating uncooked food adds 5 Poison.</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr"/>
@@ -2305,7 +2289,7 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>Get one Balloon Bunch at the next campfire. Once per run.</t>
+          <t>Get a mythic item (of your choice) at the next campfire. Once per run.</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr"/>
@@ -2344,7 +2328,7 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Get a Bandage at each new campfire after picking this card.</t>
+          <t>Get a bandage, random food item, and a random item at each new campfire after picking this card.</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr"/>
@@ -2383,14 +2367,10 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Immediately gain 2 random bonus cards.</t>
-        </is>
-      </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>One permanent random penalty: climbing or sprinting cost +10%, Injury +10%, or Hunger buildup +10%. It stays even if you give this card up.</t>
-        </is>
-      </c>
+          <t>Immediately gain 2 random bonus cards right now.</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr"/>
       <c r="I41" s="6" t="inlineStr"/>
       <c r="J41" s="6" t="inlineStr"/>
       <c r="K41" s="4" t="inlineStr">
@@ -2430,7 +2410,7 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>You and teammates within 8 m use 10% less climbing stamina.</t>
+          <t>You and teammates within 8 m use 20% less climbing stamina.</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
@@ -2473,7 +2453,7 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Healing items used on teammates remove 100% more Injury.</t>
+          <t>Healing items used on teammates and yourself remove 100% more Injury.</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr"/>
@@ -2511,7 +2491,7 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>Human Carry-On</t>
+          <t>Carry-On Scout</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -2554,7 +2534,7 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>Happy Camper Huddle</t>
+          <t>Ascent 5+</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
@@ -2598,7 +2578,7 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>First teammate revive by feeding or statue each biome: both gain 100 yellow stamina.</t>
+          <t>First teammate revive by feeding or statue each biome: both gain a full bar of yellow stamina.</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr"/>
@@ -2641,7 +2621,7 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>Pull teammates up from 30% farther away.</t>
+          <t>Pull teammates up from 40% farther away.</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
@@ -2684,12 +2664,12 @@
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>Teammates within 6 m take 30% less Injury.</t>
+          <t>Teammates within 8 m take 50% less Injury.</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>You take a quarter of the prevented Injury, up to 5 per hit.</t>
+          <t>You take a tiny amount of the prevented Injury, up to 5 per hit.</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr"/>
@@ -2722,7 +2702,7 @@
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>Friendship Bugle Choir</t>
+          <t>Friendship Bugles</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
@@ -2809,7 +2789,7 @@
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>Gain 40 yellow stamina now, then 30 at each later campfire.</t>
+          <t>Gain a full bar of yellow stamina now, then again at each later campfire.</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
@@ -2847,19 +2827,15 @@
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>Pandora's Pocket Gamble</t>
+          <t>Pandora's HotPocket</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>Inventory items weigh 10% less. Each biome: 65% chance of 25 yellow stamina.</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>A failed roll adds 7.5 Injury instead.</t>
-        </is>
-      </c>
+          <t>Inventory items weigh 25% less, and you gain 37.5 yellow stamina at each new biome.</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr"/>
       <c r="I52" s="6" t="inlineStr"/>
       <c r="J52" s="6" t="inlineStr"/>
       <c r="K52" s="4" t="inlineStr"/>
@@ -2895,7 +2871,7 @@
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>Press {key} to gain 60 yellow stamina. Once per biome.</t>
+          <t>Press {key} to gain a full bar of yellow stamina. Once per biome.</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
@@ -2945,11 +2921,7 @@
           <t>Sprint for 2s to move 30% faster until you stop.</t>
         </is>
       </c>
-      <c r="H54" s="6" t="inlineStr">
-        <is>
-          <t>Stopping after a boost adds 2.5 Drowsy, at most once every 60s.</t>
-        </is>
-      </c>
+      <c r="H54" s="6" t="inlineStr"/>
       <c r="I54" s="6" t="inlineStr"/>
       <c r="J54" s="6" t="inlineStr"/>
       <c r="K54" s="4" t="inlineStr"/>
@@ -3070,11 +3042,7 @@
           <t>Without a backpack: sprint 30% faster and jump 20% higher.</t>
         </is>
       </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>With a backpack: sprint 5% slower.</t>
-        </is>
-      </c>
+      <c r="H57" s="6" t="inlineStr"/>
       <c r="I57" s="6" t="inlineStr"/>
       <c r="J57" s="6" t="inlineStr"/>
       <c r="K57" s="4" t="inlineStr"/>
@@ -3148,12 +3116,12 @@
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>BingBong Baggage Scanner</t>
+          <t>TSA</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>Mark food, items and luggage within 12 m, even through terrain.</t>
+          <t>Mark food, items and luggage within 56 m, even through terrain.</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr"/>
@@ -3196,7 +3164,7 @@
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>At 20+ Injury, eating food removes 7.5 Injury.</t>
+          <t>At 20+ Injury, eating food heals 7.5 health.</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr"/>
@@ -3238,11 +3206,7 @@
           <t>Press {key} on flat ground: your next pass-out revives you here. Once per biome.</t>
         </is>
       </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>The revival leaves 40 Injury.</t>
-        </is>
-      </c>
+      <c r="H61" s="6" t="inlineStr"/>
       <c r="I61" s="6" t="inlineStr"/>
       <c r="J61" s="6" t="inlineStr"/>
       <c r="K61" s="4" t="inlineStr"/>
@@ -3317,7 +3281,7 @@
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>Sacrifice one of your cards to gain 35 maximum stamina.</t>
+          <t>Sacrifice one of your cards to gain 35 (MORE) maximum stamina.</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
@@ -3479,7 +3443,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>[["climbStamina", "mul", 0.88, "always", "self"], ["sprintStamina", "mul", 1.05, "always", "self"]]</t>
+          <t>[["climbStamina", "mul", 0.82, "always", "self"], ["sprintStamina", "mul", 1.1, "always", "self"]]</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr"/>
@@ -3500,7 +3464,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>[["jumpHeight", "mul", 1.3, "always", "self"], ["fallInjury", "mul", 1.15, "always", "self"]]</t>
+          <t>[["jumpHeight", "mul", 1.3, "always", "self"], ["fallInjury", "mul", 1.05, "always", "self"]]</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr"/>
@@ -3552,7 +3516,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>{"regenPerSecond": 0.1}</t>
+          <t>{"regenPerSecond": 0.05}</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3541,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>{"cooldown": 15, "drowsy": 0.05}</t>
+          <t>{"cooldown": 15}</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3556,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>[["climbSpeed", "mul", 1.3, "always", "self"], ["climbStamina", "mul", 1.2, "always", "self"]]</t>
+          <t>[["climbSpeed", "mul", 1.3, "always", "self"], ["climbStamina", "mul", 1.1, "always", "self"]]</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr"/>
@@ -3655,7 +3619,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>[["maxStamina", "add", 0.25, "always", "self"], ["hungerRate", "mul", 1.15, "always", "self"]]</t>
+          <t>[["maxStamina", "add", 0.3, "always", "self"], ["hungerRate", "mul", 1.15, "always", "self"]]</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr"/>
@@ -3686,7 +3650,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>{"threshold": 0.2, "restore": 0.3, "cooldown": 180}</t>
+          <t>{"restore": 0.3, "cooldown": 300}</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3721,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>{"hold": 3, "bonus": 0.25}</t>
+          <t>{"hold": 3, "bonus": 1.0}</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3736,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>[["sprintSpeed", "mul", 1.35, "always", "self"], ["maxStamina", "add", -0.025, "always", "self"]]</t>
+          <t>[["sprintSpeed", "mul", 1.35, "always", "self"]]</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr"/>
@@ -3803,7 +3767,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>{"buildup": 2, "boost": 2}</t>
+          <t>{"buildup": 2, "boost": 3.5}</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3782,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>[["cookedFoodHunger", "mul", 0.9, "always", "self"]]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -3906,7 +3870,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>[["sporesRate", "mul", 0.2, "always", "self"], ["poisonRate", "mul", 0.85, "always", "self"]]</t>
+          <t>[["sporesRate", "mul", 0.2, "always", "self"], ["poisonRate", "mul", 0.55, "always", "self"]]</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr"/>
@@ -3927,7 +3891,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>[["thornsRate", "mul", 0.2, "always", "self"], ["thornRemovalTime", "mul", 0.5, "always", "self"], ["nonFallInjury", "mul", 0.8, "always", "self"]]</t>
+          <t>[["thornsRate", "mul", 0.2, "always", "self"], ["thornRemovalTime", "mul", 0.5, "always", "self"]]</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr"/>
@@ -3990,13 +3954,17 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>[["climbStamina", "mul", 0.6, "poisonAbove20", "self"], ["poisonDecay", "mul", 0.9, "always", "self"]]</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>GasImmunity</t>
+        </is>
+      </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"gasThreshold": 0.02, "hit": 1.2}</t>
         </is>
       </c>
     </row>
@@ -4036,13 +4004,17 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>[["healReceived", "mul", 1.6, "always", "self"]]</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>BandageBrace</t>
+        </is>
+      </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"base": 0.2, "perBandage": 0.2, "limit": 3}</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4029,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>[["climbStamina", "mul", 0.75, "injury20", "self"], ["sprintStamina", "mul", 0.75, "injury20", "self"], ["allInjury", "mul", 1.05, "always", "self"]]</t>
+          <t>[["climbStamina", "mul", 0.65, "injury20", "self"], ["sprintStamina", "mul", 0.65, "injury20", "self"], ["allInjury", "mul", 1.05, "always", "self"]]</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr"/>
@@ -4128,7 +4100,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>[["foodHunger", "mul", 1.2, "always", "self"]]</t>
+          <t>[["foodHunger", "mul", 1.25, "always", "self"]]</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr"/>
@@ -4149,13 +4121,17 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>[["reviveCurse", "mul", 0, "always", "self"]]</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>BoneBook</t>
+        </is>
+      </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"item": 3}</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4156,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>{"bonus": 0.075}</t>
+          <t>{"min": 0.025, "max": 0.125}</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4171,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>[["totalWeight", "mul", 0.5, "always", "self"]]</t>
+          <t>[["totalWeight", "mul", 0.4, "always", "self"]]</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -4241,7 +4217,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>[["heldItemWeight", "mul", 0.35, "always", "self"], ["climbStamina", "mul", 0.85, "climbingWithItem", "self"]]</t>
+          <t>[["heldItemWeight", "mul", 0.25, "always", "self"]]</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr"/>
@@ -4262,7 +4238,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>[["cookedFoodHunger", "mul", 1.3, "always", "self"], ["uncookedFoodHunger", "mul", 0.85, "always", "self"]]</t>
+          <t>[["cookedFoodHunger", "mul", 1.4, "always", "self"], ["uncookedFoodHunger", "mul", 0.85, "always", "self"]]</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -4287,7 +4263,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>[["cookedFoodHunger", "mul", 1.5, "always", "self"]]</t>
+          <t>[["cookedFoodHunger", "mul", 1.6, "always", "self"]]</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -4317,12 +4293,12 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>NextCampfireSpawn</t>
+          <t>MythicChoice</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>{"item": 2}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4348,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>{"bonusCards": 2, "climbPenalty": 1.1, "sprintPenalty": 1.1, "injuryPenalty": 1.1, "hungerPenalty": 1.1}</t>
+          <t>{"bonusCards": 2}</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4363,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>[["climbStamina", "mul", 0.9, "always", "team"], ["climbStamina", "mul", 0.9, "teammateNear", "self"], ["climbStamina", "mul", 1.05, "noTeammateNear", "self"]]</t>
+          <t>[["climbStamina", "mul", 0.8, "always", "team"], ["climbStamina", "mul", 0.8, "teammateNear", "self"], ["climbStamina", "mul", 1.05, "noTeammateNear", "self"]]</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr"/>
@@ -4408,7 +4384,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>[["healGiven", "mul", 2.0, "always", "self"]]</t>
+          <t>[["healGiven", "mul", 2.0, "always", "self"], ["healSelfUse", "mul", 2.0, "always", "self"]]</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr"/>
@@ -4496,7 +4472,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>[["helpReach", "mul", 1.3, "always", "self"]]</t>
+          <t>[["helpReach", "mul", 1.4, "always", "self"]]</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -4521,7 +4497,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>[["allInjury", "mul", 0.7, "always", "team"]]</t>
+          <t>[["allInjury", "mul", 0.5, "always", "team"]]</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -4531,7 +4507,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>{"radius": 6, "absorb": 0.25, "cap": 0.05}</t>
+          <t>{"radius": 8, "absorb": 0.1, "cap": 0.05}</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4574,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>{"bonusNow": 0.4, "bonusFire": 0.3, "curseNow": 0.03, "curseFire": 0.01, "curseBudget": 0.05}</t>
+          <t>{"bonusNow": 1.0, "bonusFire": 1.0, "curseNow": 0.03, "curseFire": 0.01, "curseBudget": 0.05}</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4589,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>[["itemWeight", "mul", 0.9, "always", "self"]]</t>
+          <t>[["itemWeight", "mul", 0.75, "always", "self"]]</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -4623,7 +4599,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>{"chance": 0.65, "bonus": 0.25, "injury": 0.075}</t>
+          <t>{"chance": 1.0, "bonus": 0.375}</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4624,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>{"bonus": 0.6, "injury": 0.15}</t>
+          <t>{"bonus": 1.0, "injury": 0.15}</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4649,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>{"buildup": 2, "drowsy": 0.025, "cooldown": 60}</t>
+          <t>{"buildup": 2}</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4710,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>[["sprintSpeed", "mul", 1.3, "noBackpack", "self"], ["jumpHeight", "mul", 1.2, "noBackpack", "self"], ["sprintSpeed", "mul", 0.95, "wearingBackpack", "self"]]</t>
+          <t>[["sprintSpeed", "mul", 1.3, "noBackpack", "self"], ["jumpHeight", "mul", 1.2, "noBackpack", "self"]]</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr"/>
@@ -4790,7 +4766,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>{"radius": 12}</t>
+          <t>{"radius": 56}</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4816,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>{"injury": 0.4}</t>
+          <t>{"injury": 0}</t>
         </is>
       </c>
     </row>

--- a/design/editable/card-editing.xlsx
+++ b/design/editable/card-editing.xlsx
@@ -741,7 +741,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>legendary</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Hang still on a wall to recover 5 stamina per second.</t>
+          <t>Hang still on a wall to recover 7.5 stamina per second.</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>legendary</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Held items weigh 75% less.</t>
+          <t>Held items weigh 65% less.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr"/>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>legendary</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>legendary</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>legendary</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>legendary</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>{"regenPerSecond": 0.05}</t>
+          <t>{"regenPerSecond": 0.075}</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>[["heldItemWeight", "mul", 0.25, "always", "self"]]</t>
+          <t>[["heldItemWeight", "mul", 0.35, "always", "self"]]</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr"/>

--- a/design/editable/card-editing.xlsx
+++ b/design/editable/card-editing.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>PEAK target: 2.6.b. Source: design/cards.json, mod 0.8.0. All 64 cards are included. See card-edit-review.xlsx for your submitted requests and their implementation status.</t>
+          <t>PEAK target: 2.6.b. Source: design/cards.json, mod 0.9.0. All 64 cards are included. See card-edit-review.xlsx for your submitted requests and their implementation status.</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>legendary</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>Mark food, items and luggage within 56 m, even through terrain.</t>
+          <t>Hold {key} to mark food / luggage / other items within 56 m, even through terrain.</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr"/>

--- a/design/editable/card-editing.xlsx
+++ b/design/editable/card-editing.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>PEAK target: 2.6.b. Source: design/cards.json, mod 0.9.0. All 64 cards are included. See card-edit-review.xlsx for your submitted requests and their implementation status.</t>
+          <t>PEAK target: 2.6.b. Source: design/cards.json, mod 0.9.1. All 64 cards are included. See card-edit-review.xlsx for your submitted requests and their implementation status.</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Keep {key} in manual card text: the game replaces it with your configured binding. Defaults: Nic of Time V, Discount Cure-All K, Bootleg Scoutmaster Bugle B, Budget Checkpoint Flag N.</t>
+          <t>Keep {key} in manual card text: the game replaces it with your configured binding. Defaults: Nic of Time V, Discount Cure-All K, Bootleg Scoutmaster Bugle B, Budget Checkpoint Flag N; TSA shows its three held reveal keys (Y / U / I).</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>You and scouts within 15 m: maximum stamina +35; Injury and status buildup -60%. Share 1 auto-revive per biome.</t>
+          <t>You and scouts within 15 m: maximum stamina +35; Injury and status buildup -60%. Share 1 auto-revive on death per biome.</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr"/>
